--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1185,164 +1185,196 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Technician time charged, January</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>Workings!B315</f>
+        <v/>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>67.3% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Materials charged, January</t>
+        </is>
+      </c>
+      <c r="B76" s="8">
+        <f>Workings!B327</f>
+        <v/>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>$7,930 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>Workings!B314</f>
-        <v/>
-      </c>
-      <c r="C78" s="11">
-        <f>Workings!B313</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (11)</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>Workings!B325</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>Workings!B324</f>
-        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2-hour call-outs (8)</t>
+          <t>1-hour call-outs (7)</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B336</f>
+        <f>Workings!B340</f>
         <v/>
       </c>
       <c r="C80" s="11">
-        <f>Workings!B335</f>
+        <f>Workings!B339</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (11)</t>
+          <t>1.5-hour call-outs (11)</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B347</f>
+        <f>Workings!B353</f>
         <v/>
       </c>
       <c r="C81" s="11">
-        <f>Workings!B346</f>
+        <f>Workings!B352</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3-hour call-outs (21)</t>
+          <t>2-hour call-outs (8)</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B358</f>
+        <f>Workings!B366</f>
         <v/>
       </c>
       <c r="C82" s="11">
-        <f>Workings!B357</f>
+        <f>Workings!B365</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B83" s="8">
+        <f>Workings!B379</f>
+        <v/>
+      </c>
+      <c r="C83" s="11">
+        <f>Workings!B378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (21)</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B392</f>
+        <v/>
+      </c>
+      <c r="C84" s="11">
+        <f>Workings!B391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>4-hour call-outs (4)</t>
         </is>
       </c>
-      <c r="B83" s="8">
-        <f>Workings!B369</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B368</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="B85" s="8">
+        <f>Workings!B405</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B404</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="45" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>62 call-outs in January made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>62 call-outs in January billed $21,171 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Call-outs: 43.3% gross margin, 4.8 points clear of the 38.4% overheads need.</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
@@ -1350,8 +1382,8 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
@@ -1382,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3920,14 +3952,14 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>1-hour call-outs (7)</t>
+          <t>Call-out revenue, January</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="12" t="inlineStr">
         <is>
-          <t>Call-outs of this length in January, added together</t>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -3942,498 +3974,818 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B309" s="13" t="n">
-        <v>7</v>
+        <v>21171</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B310" s="13" t="n">
-        <v>2159</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B311" s="13" t="n">
-        <v>-880</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B311" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B312" s="13" t="n">
-        <v>-476</v>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B312" s="13">
+        <f>B310*(1+B311)</f>
+        <v/>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B313" s="13">
-        <f>B310+B311+B312</f>
-        <v/>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B313" s="13" t="n">
+        <v>10309</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B314" s="16">
-        <f>B313/B310</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315"/>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B314" s="13">
+        <f>B309+B313</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B315" s="16">
+        <f>B309/B314</f>
+        <v/>
+      </c>
+    </row>
     <row r="316"/>
-    <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
+    <row r="317"/>
     <row r="318">
-      <c r="A318" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, January</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="6" t="inlineStr"/>
-      <c r="B319" s="7" t="inlineStr">
+      <c r="A319" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="6" t="inlineStr"/>
+      <c r="B320" s="7" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B320" s="13" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B321" s="13" t="n">
-        <v>4528</v>
+        <v>21171</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>-1640</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B323" s="13" t="n">
-        <v>-1122</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B323" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
       <c r="B324" s="13">
-        <f>B321+B322+B323</f>
+        <f>B322*(1+B323)</f>
         <v/>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B325" s="16">
-        <f>B324/B321</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328">
-      <c r="A328" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="12" t="inlineStr">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B325" s="13" t="n">
+        <v>10309</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B326" s="13">
+        <f>B321+B325</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B327" s="16">
+        <f>B321/B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="6" t="inlineStr"/>
-      <c r="B330" s="7" t="inlineStr">
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr"/>
+      <c r="B332" s="7" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B331" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B332" s="13" t="n">
-        <v>3451</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Call-outs</t>
         </is>
       </c>
       <c r="B333" s="13" t="n">
-        <v>-870</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B334" s="13" t="n">
-        <v>-1088</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B335" s="13" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B336" s="13">
+        <f>B334+B335</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="n">
+        <v>-880</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="n">
+        <v>-476</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B335" s="13">
-        <f>B332+B333+B334</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="15" t="inlineStr">
+      <c r="B339" s="13">
+        <f>B336+B337+B338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B336" s="16">
-        <f>B335/B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339">
-      <c r="A339" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="12" t="inlineStr">
+      <c r="B340" s="16">
+        <f>B339/B336</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" s="6" t="inlineStr"/>
-      <c r="B341" s="7" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr"/>
+      <c r="B345" s="7" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B342" s="13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B343" s="13" t="n">
-        <v>6286</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B344" s="13" t="n">
-        <v>-1770</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B345" s="13" t="n">
-        <v>-1870</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B347" s="13" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="n">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B349" s="13">
+        <f>B347+B348</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="n">
+        <v>-1640</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B351" s="13" t="n">
+        <v>-1122</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B346" s="13">
-        <f>B343+B344+B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="15" t="inlineStr">
+      <c r="B352" s="13">
+        <f>B349+B350+B351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B347" s="16">
-        <f>B346/B343</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350">
-      <c r="A350" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (21)</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="12" t="inlineStr">
+      <c r="B353" s="16">
+        <f>B352/B349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" s="6" t="inlineStr"/>
-      <c r="B352" s="7" t="inlineStr">
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr"/>
+      <c r="B358" s="7" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="B359" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="n">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B354" s="13" t="n">
-        <v>12034</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B355" s="13" t="n">
-        <v>-2230</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B356" s="13" t="n">
-        <v>-4284</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B357" s="13">
-        <f>B354+B355+B356</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B358" s="16">
-        <f>B357/B354</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361">
-      <c r="A361" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
+      <c r="B362" s="13">
+        <f>B360+B361</f>
+        <v/>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="6" t="inlineStr"/>
-      <c r="B363" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="n">
+        <v>-870</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time at cost</t>
         </is>
       </c>
       <c r="B364" s="13" t="n">
-        <v>4</v>
+        <v>-1088</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B365" s="13">
+        <f>B362+B363+B364</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B366" s="16">
+        <f>B365/B362</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr"/>
+      <c r="B371" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B372" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B373" s="13" t="n">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B365" s="13" t="n">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B366" s="13" t="n">
+      <c r="B375" s="13">
+        <f>B373+B374</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="n">
+        <v>-1770</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B377" s="13" t="n">
+        <v>-1870</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B378" s="13">
+        <f>B375+B376+B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B379" s="16">
+        <f>B378/B375</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr"/>
+      <c r="B384" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B385" s="13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="n">
+        <v>9135</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B388" s="13">
+        <f>B386+B387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B389" s="13" t="n">
+        <v>-2230</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="n">
+        <v>-4284</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B391" s="13">
+        <f>B388+B389+B390</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B392" s="16">
+        <f>B391/B388</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr"/>
+      <c r="B397" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B398" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B401" s="13">
+        <f>B399+B400</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="n">
         <v>-540</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
+      <c r="B403" s="13" t="n">
         <v>-1088</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B368" s="13">
-        <f>B365+B366+B367</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="15" t="inlineStr">
+      <c r="B404" s="13">
+        <f>B401+B402+B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B369" s="16">
-        <f>B368/B365</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
+      <c r="B405" s="16">
+        <f>B404/B401</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4446,7 +4798,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="14" manualBreakCount="14">
+  <rowBreaks count="15" manualBreakCount="15">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="57" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
@@ -4459,8 +4811,9 @@
     <brk id="257" min="0" max="16383" man="1"/>
     <brk id="283" min="0" max="16383" man="1"/>
     <brk id="305" min="0" max="16383" man="1"/>
-    <brk id="327" min="0" max="16383" man="1"/>
-    <brk id="349" min="0" max="16383" man="1"/>
+    <brk id="329" min="0" max="16383" man="1"/>
+    <brk id="355" min="0" max="16383" man="1"/>
+    <brk id="381" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -25,48 +25,58 @@
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -99,36 +109,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1393,8 +1403,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4791,8 +4801,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6884,8 +6894,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Before overheads, so this is not profit. Pick a type of job and every number, chart and note on the page follows it.</t>
+          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
@@ -615,232 +615,236 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>December 37.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Job gross margin, December · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Workings!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B46</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>Workings!B45</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B55</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="8">
+        <f>Workings!B81</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>In January maintenance contracts made a 59.5% job gross margin, installations made a 23.9% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 38.4% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 23.9% gross margin, below the 38.4% needed to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Installations: 23.9% gross margin, 11.1 points under the 35.0% target: about $10,841 on $97,500 of revenue in January. It's below the 38.4% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Job gross margin, January · Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>December 59.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, January 2026</t>
+      <c r="B33" s="8">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Job gross margin, December · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wynnum medical centre</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>Workings!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C36" s="11">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
-        <f>Workings!B103</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>Workings!B102</f>
-        <v/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, January 2026</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
-        <f>Workings!B116</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>Workings!B115</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -855,7 +859,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B40" s="8">
@@ -870,7 +874,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -885,7 +889,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B42" s="8">
@@ -900,7 +904,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -915,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B44" s="8">
@@ -930,7 +934,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -945,7 +949,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -957,447 +961,571 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B47" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C47" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B48" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>The Kangaroo Point townhouses contract: 58.2% gross margin, 19.8 points clear of the 38.4% overheads need. Maintenance contracts overall: 59.5% gross margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Installations</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B229</f>
-        <v/>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>December 23.4%</t>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in January). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
         </is>
       </c>
     </row>
     <row r="57"/>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in January 2026</t>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chermside shop data cabling</t>
+          <t>Job gross margin, January · Installations</t>
         </is>
       </c>
       <c r="B60" s="8">
-        <f>Workings!B242</f>
-        <v/>
-      </c>
-      <c r="C60" s="11">
-        <f>Workings!B241</f>
-        <v/>
+        <f>Workings!B281</f>
+        <v/>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Wynnum office data cabling</t>
+          <t>Job gross margin, December · Installations</t>
         </is>
       </c>
       <c r="B61" s="8">
-        <f>Workings!B255</f>
-        <v/>
-      </c>
-      <c r="C61" s="11">
-        <f>Workings!B254</f>
-        <v/>
+        <f>Workings!B290</f>
+        <v/>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B62" s="8">
+        <f>Workings!B306</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chermside shop data cabling</t>
+        </is>
+      </c>
+      <c r="B66" s="8">
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C66" s="11">
+        <f>Workings!B319</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Wynnum office data cabling</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C67" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Milton townhouses switchboard upgrade</t>
         </is>
       </c>
-      <c r="B62" s="8">
-        <f>Workings!B268</f>
-        <v/>
-      </c>
-      <c r="C62" s="11">
-        <f>Workings!B267</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="B68" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>West End factory switchboard upgrade</t>
         </is>
       </c>
-      <c r="B63" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C63" s="11">
-        <f>Workings!B280</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B69" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Mount Gravatt clinic solar and battery</t>
         </is>
       </c>
-      <c r="B64" s="8">
-        <f>Workings!B294</f>
-        <v/>
-      </c>
-      <c r="C64" s="11">
-        <f>Workings!B293</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>4 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 10.1% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $27,000 job. Jobs need 38.4% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Below the 38.4% overheads need: Wynnum office data cabling (31.0%), Milton townhouses switchboard upgrade (24.7%), West End factory switchboard upgrade (24.0%), Mount Gravatt clinic solar and battery (10.1%). Most profitable: Chermside shop data cabling (38.9%).</t>
-        </is>
+      <c r="B70" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>Workings!B371</f>
+        <v/>
       </c>
     </row>
     <row r="71"/>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B74" s="8">
-        <f>Workings!B303</f>
-        <v/>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>December 43.5%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>4 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 10.1% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $27,000 job. Jobs need 38.4% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time charged, January</t>
-        </is>
-      </c>
-      <c r="B75" s="8">
-        <f>Workings!B315</f>
-        <v/>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>67.3% of call-out revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Materials charged, January</t>
-        </is>
-      </c>
-      <c r="B76" s="8">
-        <f>Workings!B327</f>
-        <v/>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>$7,930 at cost, plus 30%</t>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>4 installations under the 35.0% target, worth about $11,566 between them on $78,800 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 10.1% gross margin, 24.9 points under the 35.0% target: about $6,730 on $27,000 of revenue in January. It's below the 38.4% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
     <row r="77"/>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, January 2026</t>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr"/>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1-hour call-outs (7)</t>
+          <t>Job gross margin, January · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B340</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>Workings!B339</f>
-        <v/>
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (11)</t>
+          <t>Job gross margin, December · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B353</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B352</f>
-        <v/>
+        <f>Workings!B390</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2-hour call-outs (8)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B366</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>Workings!B365</f>
-        <v/>
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (11)</t>
+          <t>Technician time charged, January</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B379</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B378</f>
-        <v/>
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>67.3% of call-out revenue</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Materials charged, January</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>$7,930 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B90" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B91" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>3-hour call-outs (21)</t>
         </is>
       </c>
-      <c r="B84" s="8">
-        <f>Workings!B392</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B391</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="B92" s="8">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C92" s="11">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>4-hour call-outs (4)</t>
         </is>
       </c>
-      <c r="B85" s="8">
-        <f>Workings!B405</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B404</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="B93" s="8">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C93" s="11">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>62 call-outs in January billed $21,171 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Call-outs: 43.3% gross margin, 4.8 points clear of the 38.4% overheads need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($2,604 ahead on $31,480 in January).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96"/>
+    <row r="103"/>
+    <row r="104"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1410,10 +1538,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="47" min="0" max="16383" man="1"/>
-    <brk id="72" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="18" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
+    <brk id="63" min="0" max="16383" man="1"/>
+    <brk id="85" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1424,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C408"/>
+  <dimension ref="A1:C512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1690,14 +1819,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts, January</t>
+          <t>All lines: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1834,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1850,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>35800</v>
+        <v>164780</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>135079</v>
       </c>
     </row>
     <row r="35">
@@ -1726,7 +1863,10 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>14516</v>
+        <v>106590</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>84626</v>
       </c>
     </row>
     <row r="36">
@@ -1739,6 +1879,10 @@
         <f>B34-B35</f>
         <v/>
       </c>
+      <c r="C36" s="13">
+        <f>C34-C35</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -1748,6 +1892,10 @@
       </c>
       <c r="B37" s="16">
         <f>B36/B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>C36/C34</f>
         <v/>
       </c>
     </row>
@@ -1756,14 +1904,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Installations, January</t>
+          <t>From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -1778,407 +1926,406 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>97500</v>
+        <v>58190</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>74216</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <f>B43-B44</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>49980</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>B45/B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B46" s="13">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B43-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>58730</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs, January</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>B47-B48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>164780</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B43/B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>(B46+B48)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts, January</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>31480</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
-        <v>17858</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B54" s="13">
-        <f>B52-B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B55" s="16">
-        <f>B54/B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: gross margin, January and December</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
-        </is>
+      <c r="B60" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>35800</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>35800</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>14516</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>14516</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13">
+        <f>B60-B61</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B63" s="13">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="13">
-        <f>C61-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B64" s="16">
-        <f>B63/B61</f>
-        <v/>
-      </c>
-      <c r="C64" s="16">
-        <f>C63/C61</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B63" s="16">
+        <f>B62/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Installations, January</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>97500</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>2200</v>
+        <v>74216</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n">
-        <v>-40</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B71" s="13">
+        <f>B69-B70</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B72" s="16">
+        <f>B71/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>-B73*B74</f>
-        <v/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs, January</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>B70+B71+B72+B75</f>
-        <v/>
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>31480</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>17858</v>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>B78-B79</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>1800</v>
-      </c>
-    </row>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B81" s="16">
+        <f>B80/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>-40</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts: gross margin, January and December</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>0</v>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="n">
-        <v>10</v>
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>68</v>
+        <v>35800</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>-B86*B87</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>14516</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>14516</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>B83+B84+B85+B88</f>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B90" s="16">
-        <f>B89/B83</f>
+        <f>B89/B87</f>
+        <v/>
+      </c>
+      <c r="C90" s="16">
+        <f>C89/C87</f>
         <v/>
       </c>
     </row>
@@ -2187,14 +2334,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Maintenance contracts: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2349,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
         </is>
       </c>
     </row>
@@ -2213,187 +2365,200 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>3600</v>
+        <v>35800</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>-80</v>
+        <v>14516</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>14516</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>0</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>C96-C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>-B99*B100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98/B96</f>
+        <v/>
+      </c>
+      <c r="C99" s="16">
+        <f>C98/C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>B96+B97+B98+B101</f>
-        <v/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, January 2026</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B103" s="16">
-        <f>B102/B96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>58190</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>49980</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B108" s="13">
+        <f>B106-B107</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>3400</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>B105-B108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>-70</v>
+        <v>58730</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="n">
-        <v>0</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B111" s="13">
+        <f>B109-B110</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="n">
-        <v>19</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>164780</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B113" s="14">
+        <f>B105/B112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>-B112*B113</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="14">
+        <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B115" s="13">
-        <f>B109+B110+B111+B114</f>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>(B108+B110)/B112</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>B115/B109</f>
-        <v/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="117"/>
@@ -2401,7 +2566,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2592,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="123">
@@ -2437,7 +2602,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="124">
@@ -2457,7 +2622,7 @@
         </is>
       </c>
       <c r="B125" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126">
@@ -2508,7 +2673,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2699,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="136">
@@ -2544,7 +2709,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="137">
@@ -2564,7 +2729,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
@@ -2615,7 +2780,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2806,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="149">
@@ -2651,7 +2816,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="150">
@@ -2671,7 +2836,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -2722,7 +2887,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2913,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>4200</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="162">
@@ -2758,7 +2923,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="163">
@@ -2778,7 +2943,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165">
@@ -2829,7 +2994,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -2855,7 +3020,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>2800</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="175">
@@ -2885,7 +3050,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178">
@@ -2936,7 +3101,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3127,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>2600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="188">
@@ -2972,7 +3137,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="189">
@@ -2992,7 +3157,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191">
@@ -3043,7 +3208,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3234,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>3900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="201">
@@ -3079,7 +3244,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-110</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="202">
@@ -3099,7 +3264,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204">
@@ -3150,7 +3315,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3341,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="214">
@@ -3186,7 +3351,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="215">
@@ -3206,7 +3371,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -3257,14 +3422,14 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, January and December</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3437,7 @@
       <c r="A225" s="6" t="inlineStr"/>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="C225" s="7" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -3288,480 +3448,485 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>97500</v>
-      </c>
-      <c r="C226" s="13" t="n">
-        <v>69700</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>74216</v>
-      </c>
-      <c r="C227" s="13" t="n">
-        <v>53408</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B228" s="13">
-        <f>B226-B227</f>
-        <v/>
-      </c>
-      <c r="C228" s="13">
-        <f>C226-C227</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B229" s="16">
-        <f>B228/B226</f>
-        <v/>
-      </c>
-      <c r="C229" s="16">
-        <f>C228/C226</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230"/>
-    <row r="231"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B229" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B231" s="13">
+        <f>-B229*B230</f>
+        <v/>
+      </c>
+    </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Chermside shop data cabling</t>
-        </is>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B232" s="13">
+        <f>B226+B227+B228+B231</f>
+        <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="12" t="inlineStr">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B233" s="16">
+        <f>B232/B226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="6" t="inlineStr"/>
-      <c r="B234" s="7" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr"/>
+      <c r="B238" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B235" s="13" t="n">
-        <v>18700</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B236" s="13" t="n">
-        <v>-4300</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B237" s="13" t="n">
-        <v>-2200</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B238" s="17" t="n">
-        <v>72.5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>68</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B240" s="13">
-        <f>-B238*B239</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B242" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B244" s="13">
+        <f>-B242*B243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B241" s="13">
-        <f>B235+B236+B237+B240</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="15" t="inlineStr">
+      <c r="B245" s="13">
+        <f>B239+B240+B241+B244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B242" s="16">
-        <f>B241/B235</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum office data cabling</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="12" t="inlineStr">
+      <c r="B246" s="16">
+        <f>B245/B239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="6" t="inlineStr"/>
-      <c r="B247" s="7" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B248" s="13" t="n">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B249" s="13" t="n">
-        <v>-3300</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B250" s="13" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B251" s="17" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>68</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B253" s="13">
-        <f>-B251*B252</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B253" s="13" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B257" s="13">
+        <f>-B255*B256</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B254" s="13">
-        <f>B248+B249+B250+B253</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="15" t="inlineStr">
+      <c r="B258" s="13">
+        <f>B252+B253+B254+B257</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B255" s="16">
-        <f>B254/B248</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Milton townhouses switchboard upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="B259" s="16">
+        <f>B258/B252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr"/>
-      <c r="B260" s="7" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="n">
-        <v>13100</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="n">
-        <v>-5200</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B263" s="13" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="n">
-        <v>49.5</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>68</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B266" s="13">
-        <f>-B264*B265</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B269" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B270" s="13">
+        <f>-B268*B269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B267" s="13">
-        <f>B261+B262+B263+B266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
+      <c r="B271" s="13">
+        <f>B265+B266+B267+B270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B268" s="16">
-        <f>B267/B261</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>West End factory switchboard upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
-      <c r="B273" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B274" s="13" t="n">
-        <v>27700</v>
-      </c>
-    </row>
+      <c r="B272" s="16">
+        <f>B271/B265</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274"/>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B275" s="13" t="n">
-        <v>-10700</v>
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, January and December</t>
+        </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B276" s="13" t="n">
-        <v>-2800</v>
+      <c r="A276" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B277" s="17" t="n">
-        <v>111</v>
+      <c r="A277" s="6" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C277" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>68</v>
+        <v>97500</v>
+      </c>
+      <c r="C278" s="13" t="n">
+        <v>69700</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B279" s="13">
-        <f>-B277*B278</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B279" s="13" t="n">
+        <v>74216</v>
+      </c>
+      <c r="C279" s="13" t="n">
+        <v>53408</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B280" s="13">
-        <f>B274+B275+B276+B279</f>
+        <f>B278-B279</f>
+        <v/>
+      </c>
+      <c r="C280" s="13">
+        <f>C278-C279</f>
         <v/>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B281" s="16">
-        <f>B280/B274</f>
+        <f>B280/B278</f>
+        <v/>
+      </c>
+      <c r="C281" s="16">
+        <f>C280/C278</f>
         <v/>
       </c>
     </row>
@@ -3770,14 +3935,14 @@
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>Mount Gravatt clinic solar and battery</t>
+          <t>Installations: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3950,12 @@
       <c r="A286" s="6" t="inlineStr"/>
       <c r="B286" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C286" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
         </is>
       </c>
     </row>
@@ -3796,1006 +3966,1893 @@
         </is>
       </c>
       <c r="B287" s="13" t="n">
-        <v>27000</v>
+        <v>97500</v>
+      </c>
+      <c r="C287" s="13" t="n">
+        <v>69700</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B288" s="13" t="n">
-        <v>-13800</v>
+        <v>74216</v>
+      </c>
+      <c r="C288" s="13" t="n">
+        <v>53408</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B289" s="13" t="n">
-        <v>-3000</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B289" s="13">
+        <f>B287-B288</f>
+        <v/>
+      </c>
+      <c r="C289" s="13">
+        <f>C287-C288</f>
+        <v/>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B290" s="17" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B291" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B292" s="13">
-        <f>-B290*B291</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B290" s="16">
+        <f>B289/B287</f>
+        <v/>
+      </c>
+      <c r="C290" s="16">
+        <f>C289/C287</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291"/>
+    <row r="292"/>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B293" s="13">
-        <f>B287+B288+B289+B292</f>
-        <v/>
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, January 2026</t>
+        </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B294" s="16">
-        <f>B293/B287</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295"/>
-    <row r="296"/>
+      <c r="A294" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr"/>
+      <c r="B295" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B296" s="13" t="n">
+        <v>58190</v>
+      </c>
+    </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs: gross margin, January and December</t>
-        </is>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B297" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B298" s="13" t="n">
+        <v>49980</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr"/>
-      <c r="B299" s="7" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
-      </c>
-      <c r="C299" s="7" t="inlineStr">
-        <is>
-          <t>Dec 25</t>
-        </is>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B299" s="13">
+        <f>B297-B298</f>
+        <v/>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B300" s="13" t="n">
-        <v>31480</v>
-      </c>
-      <c r="C300" s="13" t="n">
-        <v>29579</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B300" s="13">
+        <f>B296-B299</f>
+        <v/>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B301" s="13" t="n">
-        <v>17858</v>
-      </c>
-      <c r="C301" s="13" t="n">
-        <v>16702</v>
+        <v>58730</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
       <c r="B302" s="13">
         <f>B300-B301</f>
         <v/>
       </c>
-      <c r="C302" s="13">
-        <f>C300-C301</f>
-        <v/>
-      </c>
     </row>
     <row r="303">
-      <c r="A303" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B303" s="16">
-        <f>B302/B300</f>
-        <v/>
-      </c>
-      <c r="C303" s="16">
-        <f>C302/C300</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304"/>
-    <row r="305"/>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B303" s="13" t="n">
+        <v>164780</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B304" s="14">
+        <f>B296/B303</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B305" s="14">
+        <f>B302/B303</f>
+        <v/>
+      </c>
+    </row>
     <row r="306">
-      <c r="A306" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, January</t>
-        </is>
+      <c r="A306" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B306" s="16">
+        <f>(B299+B301)/B303</f>
+        <v/>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="6" t="inlineStr"/>
-      <c r="B308" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B309" s="13" t="n">
-        <v>21171</v>
-      </c>
-    </row>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308"/>
+    <row r="309"/>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B310" s="13" t="n">
-        <v>7930</v>
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>Chermside shop data cabling</t>
+        </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B311" s="14" t="n">
-        <v>0.3</v>
+      <c r="A311" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B312" s="13">
-        <f>B310*(1+B311)</f>
-        <v/>
+      <c r="A312" s="6" t="inlineStr"/>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>10309</v>
+        <v>18700</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B314" s="13">
-        <f>B309+B313</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B314" s="13" t="n">
+        <v>-4300</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B315" s="16">
-        <f>B309/B314</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316"/>
-    <row r="317"/>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B315" s="13" t="n">
+        <v>-2200</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B316" s="17" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B317" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, January</t>
-        </is>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B318" s="13">
+        <f>-B316*B317</f>
+        <v/>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B319" s="13">
+        <f>B313+B314+B315+B318</f>
+        <v/>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr"/>
-      <c r="B320" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B321" s="13" t="n">
-        <v>21171</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B322" s="13" t="n">
-        <v>7930</v>
-      </c>
-    </row>
+      <c r="A320" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B320" s="16">
+        <f>B319/B313</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321"/>
+    <row r="322"/>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B323" s="14" t="n">
-        <v>0.3</v>
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Wynnum office data cabling</t>
+        </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B324" s="13">
-        <f>B322*(1+B323)</f>
-        <v/>
+      <c r="A324" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B325" s="13" t="n">
-        <v>10309</v>
+      <c r="A325" s="6" t="inlineStr"/>
+      <c r="B325" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B326" s="13">
-        <f>B321+B325</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B326" s="13" t="n">
+        <v>11000</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B327" s="16">
-        <f>B321/B326</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328"/>
-    <row r="329"/>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B327" s="13" t="n">
+        <v>-3300</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B328" s="13" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B329" s="17" t="n">
+        <v>44</v>
+      </c>
+    </row>
     <row r="330">
-      <c r="A330" s="5" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B331" s="13">
+        <f>-B329*B330</f>
+        <v/>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="6" t="inlineStr"/>
-      <c r="B332" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B332" s="13">
+        <f>B326+B327+B328+B331</f>
+        <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B334" s="13" t="n">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B335" s="13" t="n">
-        <v>1144</v>
-      </c>
-    </row>
+      <c r="A333" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B333" s="16">
+        <f>B332/B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334"/>
+    <row r="335"/>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B336" s="13">
-        <f>B334+B335</f>
-        <v/>
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Milton townhouses switchboard upgrade</t>
+        </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B337" s="13" t="n">
-        <v>-880</v>
+      <c r="A337" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B338" s="13" t="n">
-        <v>-476</v>
+      <c r="A338" s="6" t="inlineStr"/>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="n">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="n">
+        <v>-5200</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B342" s="17" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B344" s="13">
+        <f>-B342*B343</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B339" s="13">
-        <f>B336+B337+B338</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="15" t="inlineStr">
+      <c r="B345" s="13">
+        <f>B339+B340+B341+B344</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B340" s="16">
-        <f>B339/B336</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343">
-      <c r="A343" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="6" t="inlineStr"/>
-      <c r="B345" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B346" s="13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B347" s="13" t="n">
-        <v>2396</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="n">
-        <v>2132</v>
-      </c>
-    </row>
+      <c r="B346" s="16">
+        <f>B345/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347"/>
+    <row r="348"/>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B349" s="13">
-        <f>B347+B348</f>
-        <v/>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>West End factory switchboard upgrade</t>
+        </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="n">
-        <v>-1640</v>
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="n">
-        <v>-1122</v>
+      <c r="A351" s="6" t="inlineStr"/>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="n">
+        <v>27700</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="n">
+        <v>-10700</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="n">
+        <v>-2800</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B355" s="17" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B357" s="13">
+        <f>-B355*B356</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B352" s="13">
-        <f>B349+B350+B351</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="15" t="inlineStr">
+      <c r="B358" s="13">
+        <f>B352+B353+B354+B357</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B353" s="16">
-        <f>B352/B349</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="6" t="inlineStr"/>
-      <c r="B358" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="n">
-        <v>2320</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B361" s="13" t="n">
-        <v>1131</v>
-      </c>
-    </row>
+      <c r="B359" s="16">
+        <f>B358/B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360"/>
+    <row r="361"/>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B362" s="13">
-        <f>B360+B361</f>
-        <v/>
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>Mount Gravatt clinic solar and battery</t>
+        </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B363" s="13" t="n">
-        <v>-870</v>
+      <c r="A363" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="n">
-        <v>-1088</v>
+      <c r="A364" s="6" t="inlineStr"/>
+      <c r="B364" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="n">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="n">
+        <v>-13800</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B367" s="13" t="n">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B368" s="17" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B370" s="13">
+        <f>-B368*B369</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B365" s="13">
-        <f>B362+B363+B364</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="15" t="inlineStr">
+      <c r="B371" s="13">
+        <f>B365+B366+B367+B370</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B366" s="16">
-        <f>B365/B362</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="6" t="inlineStr"/>
-      <c r="B371" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B372" s="13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B373" s="13" t="n">
-        <v>3985</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="n">
-        <v>2301</v>
-      </c>
-    </row>
+      <c r="B372" s="16">
+        <f>B371/B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373"/>
+    <row r="374"/>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B375" s="13">
-        <f>B373+B374</f>
-        <v/>
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, January and December</t>
+        </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="n">
-        <v>-1770</v>
+      <c r="A376" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B377" s="13" t="n">
-        <v>-1870</v>
+      <c r="A377" s="6" t="inlineStr"/>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C377" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B378" s="13">
-        <f>B375+B376+B377</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B378" s="13" t="n">
+        <v>31480</v>
+      </c>
+      <c r="C378" s="13" t="n">
+        <v>29579</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B379" s="16">
-        <f>B378/B375</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382">
-      <c r="A382" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (21)</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
-      </c>
-    </row>
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B379" s="13" t="n">
+        <v>17858</v>
+      </c>
+      <c r="C379" s="13" t="n">
+        <v>16702</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B380" s="13">
+        <f>B378-B379</f>
+        <v/>
+      </c>
+      <c r="C380" s="13">
+        <f>C378-C379</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B381" s="16">
+        <f>B380/B378</f>
+        <v/>
+      </c>
+      <c r="C381" s="16">
+        <f>C380/C378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382"/>
+    <row r="383"/>
     <row r="384">
-      <c r="A384" s="6" t="inlineStr"/>
-      <c r="B384" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B385" s="13" t="n">
-        <v>21</v>
+      <c r="A385" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B386" s="13" t="n">
-        <v>9135</v>
+      <c r="A386" s="6" t="inlineStr"/>
+      <c r="B386" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
+      </c>
+      <c r="C386" s="7" t="inlineStr">
+        <is>
+          <t>Dec 25</t>
+        </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B387" s="13" t="n">
-        <v>2899</v>
+        <v>31480</v>
+      </c>
+      <c r="C387" s="13" t="n">
+        <v>29579</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B388" s="13">
-        <f>B386+B387</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B388" s="13" t="n">
+        <v>17858</v>
+      </c>
+      <c r="C388" s="13" t="n">
+        <v>16702</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B389" s="13" t="n">
-        <v>-2230</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B389" s="13">
+        <f>B387-B388</f>
+        <v/>
+      </c>
+      <c r="C389" s="13">
+        <f>C387-C388</f>
+        <v/>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B390" s="13" t="n">
-        <v>-4284</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B391" s="13">
-        <f>B388+B389+B390</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B392" s="16">
-        <f>B391/B388</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393"/>
-    <row r="394"/>
+      <c r="A390" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B390" s="16">
+        <f>B389/B387</f>
+        <v/>
+      </c>
+      <c r="C390" s="16">
+        <f>C389/C387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
     <row r="395">
-      <c r="A395" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (4)</t>
+      <c r="A395" s="6" t="inlineStr"/>
+      <c r="B395" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in January, added together</t>
-        </is>
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B396" s="13" t="n">
+        <v>58190</v>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="6" t="inlineStr"/>
-      <c r="B397" s="7" t="inlineStr">
-        <is>
-          <t>Jan 2026</t>
-        </is>
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B397" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
       <c r="B398" s="13" t="n">
-        <v>4</v>
+        <v>49980</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B399" s="13" t="n">
-        <v>2320</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B399" s="13">
+        <f>B397-B398</f>
+        <v/>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B400" s="13" t="n">
-        <v>702</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B400" s="13">
+        <f>B396-B399</f>
+        <v/>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B401" s="13">
-        <f>B399+B400</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B401" s="13" t="n">
+        <v>58730</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B402" s="13" t="n">
-        <v>-540</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B402" s="13">
+        <f>B400-B401</f>
+        <v/>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B403" s="13" t="n">
-        <v>-1088</v>
+        <v>164780</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B404" s="14">
+        <f>B396/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B405" s="14">
+        <f>B402/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B406" s="16">
+        <f>(B399+B401)/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, January</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr"/>
+      <c r="B412" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="n">
+        <v>21171</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B414" s="13" t="n">
+        <v>7930</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B415" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B416" s="13">
+        <f>B414*(1+B415)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B417" s="13" t="n">
+        <v>10309</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B418" s="13">
+        <f>B413+B417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B419" s="16">
+        <f>B413/B418</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, January</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr"/>
+      <c r="B424" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="n">
+        <v>21171</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B426" s="13" t="n">
+        <v>7930</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B427" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B428" s="13">
+        <f>B426*(1+B427)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B429" s="13" t="n">
+        <v>10309</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B430" s="13">
+        <f>B425+B429</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B431" s="16">
+        <f>B425/B430</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr"/>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B437" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B438" s="13" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B439" s="13" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B440" s="13">
+        <f>B438+B439</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B441" s="13" t="n">
+        <v>-880</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="n">
+        <v>-476</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B404" s="13">
-        <f>B401+B402+B403</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="15" t="inlineStr">
+      <c r="B443" s="13">
+        <f>B440+B441+B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B405" s="16">
-        <f>B404/B401</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
+      <c r="B444" s="16">
+        <f>B443/B440</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr"/>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B450" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B451" s="13" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="n">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B453" s="13">
+        <f>B451+B452</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B454" s="13" t="n">
+        <v>-1640</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B455" s="13" t="n">
+        <v>-1122</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B456" s="13">
+        <f>B453+B454+B455</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B457" s="16">
+        <f>B456/B453</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr"/>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B463" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B464" s="13" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B465" s="13" t="n">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B466" s="13">
+        <f>B464+B465</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B467" s="13" t="n">
+        <v>-870</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B468" s="13" t="n">
+        <v>-1088</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B469" s="13">
+        <f>B466+B467+B468</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B470" s="16">
+        <f>B469/B466</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr"/>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B476" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B477" s="13" t="n">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B478" s="13" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B479" s="13">
+        <f>B477+B478</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="n">
+        <v>-1770</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="n">
+        <v>-1870</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B482" s="13">
+        <f>B479+B480+B481</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B483" s="16">
+        <f>B482/B479</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr"/>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B489" s="13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B490" s="13" t="n">
+        <v>9135</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B491" s="13" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B492" s="13">
+        <f>B490+B491</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B493" s="13" t="n">
+        <v>-2230</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B494" s="13" t="n">
+        <v>-4284</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B495" s="13">
+        <f>B492+B493+B494</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B496" s="16">
+        <f>B495/B492</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in January, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr"/>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B502" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B503" s="13" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B504" s="13" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B505" s="13">
+        <f>B503+B504</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B506" s="13" t="n">
+        <v>-540</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B507" s="13" t="n">
+        <v>-1088</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B508" s="13">
+        <f>B505+B506+B507</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B509" s="16">
+        <f>B508/B505</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4808,22 +5865,26 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="15" manualBreakCount="15">
+  <rowBreaks count="19" manualBreakCount="19">
     <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="57" min="0" max="16383" man="1"/>
-    <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="105" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
     <brk id="131" min="0" max="16383" man="1"/>
     <brk id="157" min="0" max="16383" man="1"/>
     <brk id="183" min="0" max="16383" man="1"/>
     <brk id="209" min="0" max="16383" man="1"/>
-    <brk id="231" min="0" max="16383" man="1"/>
-    <brk id="257" min="0" max="16383" man="1"/>
-    <brk id="283" min="0" max="16383" man="1"/>
-    <brk id="305" min="0" max="16383" man="1"/>
-    <brk id="329" min="0" max="16383" man="1"/>
-    <brk id="355" min="0" max="16383" man="1"/>
-    <brk id="381" min="0" max="16383" man="1"/>
+    <brk id="235" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="292" min="0" max="16383" man="1"/>
+    <brk id="322" min="0" max="16383" man="1"/>
+    <brk id="348" min="0" max="16383" man="1"/>
+    <brk id="374" min="0" max="16383" man="1"/>
+    <brk id="392" min="0" max="16383" man="1"/>
+    <brk id="421" min="0" max="16383" man="1"/>
+    <brk id="446" min="0" max="16383" man="1"/>
+    <brk id="472" min="0" max="16383" man="1"/>
+    <brk id="498" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -12,7 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$15</definedName>
+    <definedName name="Job_gross_margin_December_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
+    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$41</definedName>
+    <definedName name="Job_gross_margin_December_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
+    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$77</definedName>
+    <definedName name="Job_gross_margin_December_Installations">'Report'!$B$78</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$79</definedName>
+    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$103</definedName>
+    <definedName name="Job_gross_margin_December_Call_outs_and_repairs">'Report'!$B$104</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$105</definedName>
+    <definedName name="Technician_time_charged_January">'Report'!$B$106</definedName>
+    <definedName name="Materials_charged_January">'Report'!$B$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,11 +67,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -70,6 +82,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,27 +135,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +238,848 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin by type of job, January 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$21:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each maintenance contract, January 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$47:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$47:$B$58</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each installation invoiced in January 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$83:$A$87</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$83:$B$87</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on call-outs by length, January 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$111:$A$116</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$111:$B$116</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$21</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$22:$D$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$38:$D$53</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$54:$D$69</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2070000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="job_margins_Data" displayName="job_margins_Data" ref="A5:G69" headerRowCount="1">
+  <autoFilter ref="A5:G69"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -529,14 +1390,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -552,14 +1413,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>January's jobs made $58,190 gross margin (35.3%). Technician time not charged to jobs took $4,620 and overheads $58,730, leaving ($5,160) profit before tax ((3.1%) of revenue). To cover overheads, jobs need a 38.4% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -567,14 +1428,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>January's jobs made $58,190 gross margin (35.3%). Technician time not charged to jobs took $4,620 and overheads $58,730, leaving ($5,160) profit before tax ((3.1%) of revenue). To cover overheads, jobs need a 38.4% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -718,754 +1579,531 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>In January maintenance contracts made a 59.5% job gross margin, installations made a 23.9% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 38.4% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Installations: 23.9% gross margin, 11.1 points under the 35.0% target: about $10,841 on $97,500 of revenue in January. It's below the 38.4% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Job gross margin, December · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B34" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
-        <f>Workings!B115</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (January)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, January 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>Workings!B128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B40" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C40" s="11">
-        <f>Workings!B141</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Job gross margin, January · Maintenance contracts</t>
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C41" s="11">
-        <f>Workings!B154</f>
-        <v/>
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Job gross margin, December · Maintenance contracts</t>
         </is>
       </c>
       <c r="B42" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C42" s="11">
-        <f>Workings!B167</f>
-        <v/>
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B43" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>Workings!B180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B44" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C44" s="11">
-        <f>Workings!B193</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>Workings!B206</f>
-        <v/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, January 2026</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B46" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C46" s="11">
-        <f>Workings!B219</f>
-        <v/>
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B47" s="8">
-        <f>Workings!B233</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>Workings!B232</f>
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B48" s="8">
-        <f>Workings!B246</f>
+        <f>Workings!B142</f>
         <v/>
       </c>
       <c r="C48" s="11">
-        <f>Workings!B245</f>
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B49" s="8">
-        <f>Workings!B259</f>
+        <f>Workings!B155</f>
         <v/>
       </c>
       <c r="C49" s="11">
-        <f>Workings!B258</f>
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B193</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>Workings!B206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>Workings!B219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B56" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C56" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B50" s="8">
+      <c r="B58" s="8">
         <f>Workings!B272</f>
         <v/>
       </c>
-      <c r="C50" s="11">
+      <c r="C58" s="11">
         <f>Workings!B271</f>
         <v/>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in January). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Installations</t>
-        </is>
-      </c>
-      <c r="B60" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Job gross margin, December · Installations</t>
-        </is>
-      </c>
-      <c r="B61" s="8">
-        <f>Workings!B290</f>
-        <v/>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B62" s="8">
-        <f>Workings!B306</f>
-        <v/>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (January)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in January 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr"/>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Chermside shop data cabling</t>
-        </is>
-      </c>
-      <c r="B66" s="8">
-        <f>Workings!B320</f>
-        <v/>
-      </c>
-      <c r="C66" s="11">
-        <f>Workings!B319</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Wynnum office data cabling</t>
-        </is>
-      </c>
-      <c r="B67" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Milton townhouses switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B68" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>Workings!B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>West End factory switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B69" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C69" s="11">
-        <f>Workings!B358</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Mount Gravatt clinic solar and battery</t>
-        </is>
-      </c>
-      <c r="B70" s="8">
-        <f>Workings!B372</f>
-        <v/>
-      </c>
-      <c r="C70" s="11">
-        <f>Workings!B371</f>
-        <v/>
       </c>
     </row>
     <row r="71"/>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="60" customHeight="1">
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>4 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 10.1% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $27,000 job. Jobs need 38.4% gross margin just to cover overheads.</t>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in January). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
         </is>
       </c>
     </row>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>4 installations under the 35.0% target, worth about $11,566 between them on $78,800 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 10.1% gross margin, 24.9 points under the 35.0% target: about $6,730 on $27,000 of revenue in January. It's below the 38.4% needed to cover overheads, too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Job gross margin, January · Installations</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>Workings!B281</f>
+        <v/>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Job gross margin, December · Installations</t>
+        </is>
+      </c>
+      <c r="B78" s="8">
+        <f>Workings!B290</f>
+        <v/>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B80" s="8">
-        <f>Workings!B381</f>
-        <v/>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>Workings!B306</f>
+        <v/>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Job gross margin, December · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B81" s="8">
-        <f>Workings!B390</f>
-        <v/>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in January 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B82" s="8">
-        <f>Workings!B406</f>
-        <v/>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (January)</t>
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technician time charged, January</t>
+          <t>Chermside shop data cabling</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>67.3% of call-out revenue</t>
-        </is>
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C83" s="11">
+        <f>Workings!B319</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Materials charged, January</t>
+          <t>Wynnum office data cabling</t>
         </is>
       </c>
       <c r="B84" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>$7,930 at cost, plus 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C84" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Milton townhouses switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, January 2026</t>
-        </is>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>West End factory switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B86" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B358</f>
+        <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr"/>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
-      </c>
-      <c r="B88" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C88" s="11">
-        <f>Workings!B443</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (11)</t>
-        </is>
-      </c>
-      <c r="B89" s="8">
-        <f>Workings!B457</f>
-        <v/>
-      </c>
-      <c r="C89" s="11">
-        <f>Workings!B456</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (8)</t>
-        </is>
-      </c>
-      <c r="B90" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C90" s="11">
-        <f>Workings!B469</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (11)</t>
-        </is>
-      </c>
-      <c r="B91" s="8">
-        <f>Workings!B483</f>
-        <v/>
-      </c>
-      <c r="C91" s="11">
-        <f>Workings!B482</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (21)</t>
-        </is>
-      </c>
-      <c r="B92" s="8">
-        <f>Workings!B496</f>
-        <v/>
-      </c>
-      <c r="C92" s="11">
-        <f>Workings!B495</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (4)</t>
-        </is>
-      </c>
-      <c r="B93" s="8">
-        <f>Workings!B509</f>
-        <v/>
-      </c>
-      <c r="C93" s="11">
-        <f>Workings!B508</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mount Gravatt clinic solar and battery</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
     <row r="94"/>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -1477,7 +2115,7 @@
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>62 call-outs in January billed $21,171 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>4 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 10.1% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $27,000 job. Jobs need 38.4% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -1489,10 +2127,10 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="30" customHeight="1">
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($2,604 ahead on $31,480 in January).</t>
+          <t>4 installations under the 35.0% target, worth about $11,566 between them on $78,800 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 10.1% gross margin, 24.9 points under the 35.0% target: about $6,730 on $27,000 of revenue in January. It's below the 38.4% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -1500,50 +2138,305 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Job gross margin, January · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B103" s="8">
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Job gross margin, December · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B104" s="8">
+        <f>Workings!B390</f>
+        <v/>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B105" s="8">
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician time charged, January</t>
+        </is>
+      </c>
+      <c r="B106" s="8">
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>67.3% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Materials charged, January</t>
+        </is>
+      </c>
+      <c r="B107" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>$7,930 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr"/>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+      <c r="B111" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C111" s="11">
+        <f>Workings!B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B112" s="8">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C112" s="11">
+        <f>Workings!B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B113" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C113" s="11">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B114" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C114" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (21)</t>
+        </is>
+      </c>
+      <c r="B115" s="8">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C115" s="11">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B116" s="8">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C116" s="11">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>62 call-outs in January billed $21,171 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($2,604 ahead on $31,480 in January).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104"/>
+    <row r="133"/>
+    <row r="134"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A126:D126"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A129:D129"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="63" min="0" max="16383" man="1"/>
-    <brk id="85" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="68" min="0" max="16383" man="1"/>
+    <brk id="94" min="0" max="16383" man="1"/>
+    <brk id="108" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1572,14 +2465,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1587,7 +2480,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, January 2026</t>
+          <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2627,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, January and December</t>
+          <t>Trades, all lines: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -1819,7 +2712,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, January and December</t>
+          <t>Trades, all lines: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2797,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, January 2026</t>
+          <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
@@ -2249,7 +3142,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, January and December</t>
+          <t>Trades, Maintenance contracts: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -2334,7 +3227,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, January and December</t>
+          <t>Trades, Maintenance contracts: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -2419,7 +3312,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, January 2026</t>
+          <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
@@ -3850,7 +4743,7 @@
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, January and December</t>
+          <t>Trades, Installations: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -3935,7 +4828,7 @@
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, January and December</t>
+          <t>Trades, Installations: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4913,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, January 2026</t>
+          <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
@@ -4702,7 +5595,7 @@
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, January and December</t>
+          <t>Trades, Call-outs and repairs: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -4787,7 +5680,7 @@
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, January and December</t>
+          <t>Trades, Call-outs and repairs: gross margin, January and December</t>
         </is>
       </c>
     </row>
@@ -4872,7 +5765,7 @@
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, January 2026</t>
+          <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
@@ -5859,7 +6752,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5917,14 +6810,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -7956,7 +8849,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7967,5 +8860,9 @@
     <brk id="37" min="0" max="16383" man="1"/>
     <brk id="53" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$15</definedName>
@@ -28,8 +29,8 @@
     <definedName name="Materials_charged_January">'Report'!$B$107</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,7 +265,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin by type of job, January 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin by type of job, January 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,6 +332,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 38.4%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$8:$B$9</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$8:$C$9</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -346,6 +495,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -353,6 +504,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -385,7 +563,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each maintenance contract, January 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each maintenance contract, January 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,6 +616,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$12:$B$13</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$12:$C$13</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 38.4%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$16:$B$17</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$16:$C$17</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -453,6 +779,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.7026499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -460,6 +788,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.7026499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -492,7 +847,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in January 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in January 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -601,6 +956,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$20:$B$21</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$20:$C$21</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 38.4%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$24:$B$25</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$24:$C$25</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -616,6 +1119,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.44735"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -623,6 +1128,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.44735"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -655,7 +1187,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on call-outs by length, January 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on call-outs by length, January 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -708,6 +1240,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$28:$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$28:$C$29</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 38.4%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$32:$B$33</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$32:$C$33</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -723,6 +1403,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.53015"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -730,6 +1412,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.53015"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -955,7 +1664,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -977,7 +1686,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3960000"/>
+    <ext cx="5400000" cy="4176000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -999,7 +1708,7 @@
       <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2070000"/>
+    <ext cx="5400000" cy="2286000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1021,7 +1730,7 @@
       <row>109</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1397,7 +2106,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -2423,7 +3132,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2472,7 +3181,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -6752,7 +7461,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6786,6 +7495,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, January 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, January 2026: Break-even 38.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, January 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, January 2026: Break-even 38.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in January 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in January 2026: Break-even 38.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, January 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, January 2026: Break-even 38.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G69"/>
@@ -6817,7 +7739,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -8849,7 +9771,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -409,7 +409,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 38.4%</v>
+            <v>Break-even 44.2%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -495,7 +495,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.7336999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -509,7 +509,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.7336999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -693,7 +693,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 38.4%</v>
+            <v>Break-even 44.2%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -779,7 +779,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7026499999999999"/>
+          <max val="0.7486499999999998"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -793,7 +793,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7026499999999999"/>
+          <max val="0.7486499999999998"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -877,20 +877,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dPt>
             <idx val="2"/>
             <spPr>
@@ -1033,7 +1019,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 38.4%</v>
+            <v>Break-even 44.2%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1119,7 +1105,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.44735"/>
+          <max val="0.5209499999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1133,7 +1119,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.44735"/>
+          <max val="0.5209499999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1317,7 +1303,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 38.4%</v>
+            <v>Break-even 44.2%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1403,7 +1389,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.53015"/>
+          <max val="0.5841999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1417,7 +1403,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.53015"/>
+          <max val="0.5841999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2106,7 +2092,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2115,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>January's jobs made $58,190 gross margin (35.3%). Technician time not charged to jobs took $4,620 and overheads $58,730, leaving ($5,160) profit before tax ((3.1%) of revenue). To cover overheads, jobs need a 38.4% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>January's jobs made $76,716 gross margin (41.9%). Technician time not charged to jobs took $22,372 and overheads $58,730, leaving ($4,386) profit before tax ((2.4%) of revenue). To cover overheads, jobs need a 44.2% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2130,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2292,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>In January maintenance contracts made a 59.5% job gross margin, installations made a 23.9% job gross margin, call-outs and repairs made a 43.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 38.4% just to cover overheads.</t>
+          <t>In January maintenance contracts made a 63.8% job gross margin, installations made a 32.0% job gross margin, call-outs and repairs made a 47.6% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 44.2% just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2307,7 @@
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Installations: 23.9% gross margin, 11.1 points under the 35.0% target: about $10,841 on $97,500 of revenue in January. It's below the 38.4% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
+          <t>Installations: 32.0% gross margin, 3.0 points under the 35.0% target: about $3,301 on $109,100 of revenue in January. It's below the 44.2% needed to cover overheads, too. Maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in January).</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2423,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B48" s="8">
@@ -2452,7 +2438,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2467,7 +2453,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B50" s="8">
@@ -2482,7 +2468,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2497,7 +2483,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B52" s="8">
@@ -2527,7 +2513,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B54" s="8">
@@ -2542,7 +2528,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -2619,7 +2605,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
+          <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2620,7 @@
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in January). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($8,754 ahead on $35,800 in January).</t>
+          <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in January). All maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in January).</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2810,7 @@
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>4 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 10.1% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $27,000 job. Jobs need 38.4% gross margin just to cover overheads.</t>
+          <t>3 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 19.6% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $30,200 job. Jobs need 44.2% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2825,7 @@
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>4 installations under the 35.0% target, worth about $11,566 between them on $78,800 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 10.1% gross margin, 24.9 points under the 35.0% target: about $6,730 on $27,000 of revenue in January. It's below the 38.4% needed to cover overheads, too.</t>
+          <t>3 installations under the 35.0% target, worth about $5,859 between them on $75,900 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 19.6% gross margin, 15.4 points under the 35.0% target: about $4,650 on $30,200 of revenue in January. It's below the 44.2% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2914,7 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>67.3% of call-out revenue</t>
+          <t>69.8% of call-out revenue</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3063,7 @@
     <row r="126" ht="60" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>62 call-outs in January billed $21,171 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 43.3% job gross margin between them. Gross margins run from 37.2% to 46.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>62 call-outs in January billed $23,797 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 47.6% job gross margin between them. Gross margins run from 40.7% to 50.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3078,7 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 43.3% gross margin, 8.3 points over the 35.0% target ($2,604 ahead on $31,480 in January).</t>
+          <t>All call-outs: 47.6% gross margin, 12.6 points over the 35.0% target ($4,311 ahead on $34,106 in January).</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3118,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3181,7 +3167,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3201,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>58190</v>
+        <v>76716</v>
       </c>
     </row>
     <row r="9">
@@ -3225,7 +3211,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="10">
@@ -3288,7 +3274,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="16">
@@ -3327,7 +3313,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3367,10 +3353,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
     </row>
     <row r="26">
@@ -3452,10 +3438,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
     </row>
     <row r="35">
@@ -3532,7 +3518,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>58190</v>
+        <v>76716</v>
       </c>
     </row>
     <row r="44">
@@ -3542,7 +3528,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="45">
@@ -3605,7 +3591,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="51">
@@ -3644,7 +3630,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3665,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="61">
@@ -3745,7 +3731,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
     </row>
     <row r="70">
@@ -3811,7 +3797,7 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
     </row>
     <row r="79">
@@ -3882,10 +3868,10 @@
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="88">
@@ -3967,10 +3953,10 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="97">
@@ -4047,7 +4033,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>58190</v>
+        <v>76716</v>
       </c>
     </row>
     <row r="106">
@@ -4057,7 +4043,7 @@
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="107">
@@ -4120,7 +4106,7 @@
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="113">
@@ -4159,7 +4145,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4180,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="123">
@@ -4275,7 +4261,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4287,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>1800</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="136">
@@ -4311,7 +4297,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-40</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="137">
@@ -4331,7 +4317,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139">
@@ -4382,7 +4368,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4404,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="150">
@@ -4438,7 +4424,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
@@ -4489,7 +4475,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4501,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="162">
@@ -4525,7 +4511,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="163">
@@ -4545,7 +4531,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
@@ -4596,7 +4582,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4608,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="175">
@@ -4632,7 +4618,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="176">
@@ -4652,7 +4638,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178">
@@ -4703,7 +4689,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4715,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="188">
@@ -4739,7 +4725,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="189">
@@ -4759,7 +4745,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191">
@@ -4836,7 +4822,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="201">
@@ -4917,7 +4903,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4929,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>4200</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="214">
@@ -4953,7 +4939,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-90</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="215">
@@ -4973,7 +4959,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217">
@@ -5024,7 +5010,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5036,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>2800</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="227">
@@ -5060,7 +5046,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="228">
@@ -5080,7 +5066,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="230">
@@ -5157,7 +5143,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="240">
@@ -5264,7 +5250,7 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="253">
@@ -5371,7 +5357,7 @@
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="266">
@@ -5483,10 +5469,10 @@
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="C278" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="279">
@@ -5568,10 +5554,10 @@
         </is>
       </c>
       <c r="B287" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="C287" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="288">
@@ -5648,7 +5634,7 @@
         </is>
       </c>
       <c r="B296" s="13" t="n">
-        <v>58190</v>
+        <v>76716</v>
       </c>
     </row>
     <row r="297">
@@ -5658,7 +5644,7 @@
         </is>
       </c>
       <c r="B297" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="298">
@@ -5721,7 +5707,7 @@
         </is>
       </c>
       <c r="B303" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="304">
@@ -5760,7 +5746,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5781,7 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>18700</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="314">
@@ -5902,7 +5888,7 @@
         </is>
       </c>
       <c r="B326" s="13" t="n">
-        <v>11000</v>
+        <v>12300</v>
       </c>
     </row>
     <row r="327">
@@ -6009,7 +5995,7 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>13100</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="340">
@@ -6116,7 +6102,7 @@
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>27700</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="353">
@@ -6223,7 +6209,7 @@
         </is>
       </c>
       <c r="B365" s="13" t="n">
-        <v>27000</v>
+        <v>30200</v>
       </c>
     </row>
     <row r="366">
@@ -6335,10 +6321,10 @@
         </is>
       </c>
       <c r="B378" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="C378" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
     </row>
     <row r="379">
@@ -6420,10 +6406,10 @@
         </is>
       </c>
       <c r="B387" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="C387" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
     </row>
     <row r="388">
@@ -6500,7 +6486,7 @@
         </is>
       </c>
       <c r="B396" s="13" t="n">
-        <v>58190</v>
+        <v>76716</v>
       </c>
     </row>
     <row r="397">
@@ -6510,7 +6496,7 @@
         </is>
       </c>
       <c r="B397" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="398">
@@ -6573,7 +6559,7 @@
         </is>
       </c>
       <c r="B403" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="404">
@@ -6612,7 +6598,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6614,7 @@
     <row r="411">
       <c r="A411" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6643,11 +6629,11 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B413" s="13" t="n">
-        <v>21171</v>
+        <v>23797</v>
       </c>
     </row>
     <row r="414">
@@ -6725,7 +6711,7 @@
     <row r="423">
       <c r="A423" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6740,11 +6726,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B425" s="13" t="n">
-        <v>21171</v>
+        <v>23797</v>
       </c>
     </row>
     <row r="426">
@@ -6847,11 +6833,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B438" s="13" t="n">
-        <v>1015</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="439">
@@ -6954,11 +6940,11 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B451" s="13" t="n">
-        <v>2396</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="452">
@@ -7061,11 +7047,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B464" s="13" t="n">
-        <v>2320</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="465">
@@ -7168,11 +7154,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B477" s="13" t="n">
-        <v>3985</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="478">
@@ -7275,11 +7261,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B490" s="13" t="n">
-        <v>9135</v>
+        <v>10269</v>
       </c>
     </row>
     <row r="491">
@@ -7382,11 +7368,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B503" s="13" t="n">
-        <v>2320</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="504">
@@ -7461,7 +7447,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7535,13 +7521,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report: Job gross margin by type of job, January 2026: Break-even 38.4%</t>
+          <t>Report: Job gross margin by type of job, January 2026: Break-even 44.2%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7549,7 +7535,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -7583,13 +7569,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each maintenance contract, January 2026: Break-even 38.4%</t>
+          <t>Report: Job gross margin on each maintenance contract, January 2026: Break-even 44.2%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -7597,7 +7583,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -7631,13 +7617,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each installation invoiced in January 2026: Break-even 38.4%</t>
+          <t>Report: Job gross margin on each installation invoiced in January 2026: Break-even 44.2%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -7645,7 +7631,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7679,13 +7665,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on call-outs by length, January 2026: Break-even 38.4%</t>
+          <t>Report: Job gross margin on call-outs by length, January 2026: Break-even 44.2%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -7693,7 +7679,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>0.384</v>
+        <v>0.442</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -7739,7 +7725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7784,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>114334</v>
@@ -7829,7 +7815,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>113016</v>
@@ -7860,7 +7846,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>85316</v>
@@ -7891,7 +7877,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>80742</v>
@@ -7922,7 +7908,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>102348</v>
@@ -7953,7 +7939,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>85752</v>
@@ -7984,7 +7970,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>76808</v>
@@ -8015,7 +8001,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>83700</v>
@@ -8046,7 +8032,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>97584</v>
@@ -8077,7 +8063,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>120326</v>
@@ -8108,7 +8094,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>78258</v>
@@ -8139,7 +8125,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>80054</v>
@@ -8170,7 +8156,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>79452</v>
@@ -8201,7 +8187,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>115942</v>
@@ -8232,7 +8218,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>84626</v>
@@ -8263,7 +8249,7 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>106590</v>
@@ -8294,7 +8280,7 @@
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>10420</v>
@@ -8325,7 +8311,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>10420</v>
@@ -8356,7 +8342,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>10420</v>
@@ -8387,7 +8373,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>10420</v>
@@ -8418,7 +8404,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>11782</v>
@@ -8449,7 +8435,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>11782</v>
@@ -8480,7 +8466,7 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>11782</v>
@@ -8511,7 +8497,7 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>11782</v>
@@ -8542,7 +8528,7 @@
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>13446</v>
@@ -8573,7 +8559,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>13446</v>
@@ -8604,7 +8590,7 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>13446</v>
@@ -8635,7 +8621,7 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>13446</v>
@@ -8666,7 +8652,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>14516</v>
@@ -8697,7 +8683,7 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>14516</v>
@@ -8728,7 +8714,7 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>14516</v>
@@ -8759,7 +8745,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>14516</v>
@@ -8790,7 +8776,7 @@
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>92430</v>
@@ -8821,7 +8807,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>89070</v>
@@ -8852,7 +8838,7 @@
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>59908</v>
@@ -8883,7 +8869,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>54678</v>
@@ -8914,7 +8900,7 @@
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>74966</v>
@@ -8945,7 +8931,7 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>61664</v>
@@ -8976,7 +8962,7 @@
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>52264</v>
@@ -9007,7 +8993,7 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>59534</v>
@@ -9038,7 +9024,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>72976</v>
@@ -9069,7 +9055,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>96920</v>
@@ -9100,7 +9086,7 @@
         </is>
       </c>
       <c r="D48" s="13" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>53590</v>
@@ -9131,7 +9117,7 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>55440</v>
@@ -9162,7 +9148,7 @@
         </is>
       </c>
       <c r="D50" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>52288</v>
@@ -9193,7 +9179,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>87174</v>
@@ -9224,7 +9210,7 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E52" s="13" t="n">
         <v>53408</v>
@@ -9255,7 +9241,7 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>74216</v>
@@ -9286,7 +9272,7 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E54" s="13" t="n">
         <v>11484</v>
@@ -9317,7 +9303,7 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>13526</v>
@@ -9348,7 +9334,7 @@
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>14988</v>
@@ -9379,7 +9365,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>15644</v>
@@ -9410,7 +9396,7 @@
         </is>
       </c>
       <c r="D58" s="13" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E58" s="13" t="n">
         <v>15600</v>
@@ -9441,7 +9427,7 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>12306</v>
@@ -9472,7 +9458,7 @@
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E60" s="13" t="n">
         <v>12762</v>
@@ -9503,7 +9489,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>12384</v>
@@ -9534,7 +9520,7 @@
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E62" s="13" t="n">
         <v>11162</v>
@@ -9565,7 +9551,7 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>9960</v>
@@ -9596,7 +9582,7 @@
         </is>
       </c>
       <c r="D64" s="13" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E64" s="13" t="n">
         <v>11222</v>
@@ -9627,7 +9613,7 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>11168</v>
@@ -9658,7 +9644,7 @@
         </is>
       </c>
       <c r="D66" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E66" s="13" t="n">
         <v>12648</v>
@@ -9689,7 +9675,7 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>14252</v>
@@ -9720,7 +9706,7 @@
         </is>
       </c>
       <c r="D68" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E68" s="13" t="n">
         <v>16702</v>
@@ -9751,7 +9737,7 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>17858</v>
@@ -9771,7 +9757,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/job-margins.xlsx
+++ b/media/exports/reports/2026-01/job-margins.xlsx
@@ -13,21 +13,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$15</definedName>
-    <definedName name="Job_gross_margin_December_All_jobs">'Report'!$B$16</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
-    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$41</definedName>
-    <definedName name="Job_gross_margin_December_Maintenance_contracts">'Report'!$B$42</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
-    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$77</definedName>
-    <definedName name="Job_gross_margin_December_Installations">'Report'!$B$78</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$79</definedName>
-    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$103</definedName>
-    <definedName name="Job_gross_margin_December_Call_outs_and_repairs">'Report'!$B$104</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$105</definedName>
-    <definedName name="Technician_time_charged_January">'Report'!$B$106</definedName>
-    <definedName name="Materials_charged_January">'Report'!$B$107</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$132</definedName>
+    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Job_gross_margin_December_All_jobs">'Report'!$B$17</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$18</definedName>
+    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Job_gross_margin_December_Maintenance_contracts">'Report'!$B$43</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$44</definedName>
+    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$78</definedName>
+    <definedName name="Job_gross_margin_December_Installations">'Report'!$B$79</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$80</definedName>
+    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$104</definedName>
+    <definedName name="Job_gross_margin_December_Call_outs_and_repairs">'Report'!$B$105</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$106</definedName>
+    <definedName name="Technician_time_charged_January">'Report'!$B$107</definedName>
+    <definedName name="Materials_charged_January">'Report'!$B$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$133</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$69</definedName>
@@ -67,6 +67,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
@@ -92,11 +97,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,36 +129,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,12 +322,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$21:$A$23</f>
+              <f>'Report'!$A$22:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$21:$B$23</f>
+              <f>'Report'!$B$22:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -603,12 +606,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$47:$A$58</f>
+              <f>'Report'!$A$48:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$47:$B$58</f>
+              <f>'Report'!$B$48:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -929,12 +932,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$83:$A$87</f>
+              <f>'Report'!$A$84:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$83:$B$87</f>
+              <f>'Report'!$B$84:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -1213,12 +1216,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$111:$A$116</f>
+              <f>'Report'!$A$112:$A$117</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$111:$B$116</f>
+              <f>'Report'!$B$112:$B$117</f>
             </numRef>
           </val>
         </ser>
@@ -1647,7 +1650,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1669,7 +1672,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="4176000"/>
@@ -1691,7 +1694,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2286000"/>
@@ -1713,7 +1716,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2556000"/>
@@ -2066,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2092,7 +2095,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2100,92 +2103,83 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Jobs made a 41.9% gross margin in January: maintenance contracts the most (63.8%), installations the least (32.0%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>From gross margin to profit</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>January's jobs made $76,716 gross margin (41.9%). Technician time not charged to jobs took $22,372 and overheads $58,730, leaving ($4,386) profit before tax ((2.4%) of revenue). To cover overheads, jobs need a 44.2% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Gross margin, not profit</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: All jobs</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Type of job: All jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · All jobs</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Job gross margin, December · All jobs</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+          <t>Job gross margin, January · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2194,86 +2188,101 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Job gross margin, December · All jobs</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!C37</f>
+        <v/>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B18" s="9">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (January)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>Workings!B63</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B62</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>Workings!B72</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>Workings!B71</f>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B24" s="9">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="12">
         <f>Workings!B80</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -2282,87 +2291,72 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>In January maintenance contracts made a 63.8% job gross margin, installations made a 32.0% job gross margin, call-outs and repairs made a 47.6% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 44.2% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Installations: 32.0% gross margin, 3.0 points under the 35.0% target: about $3,301 on $109,100 of revenue in January. It's below the 44.2% needed to cover overheads, too. Maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in January).</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Maintenance contracts</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Maintenance contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B41" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Job gross margin, December · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B42" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>Job gross margin, January · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2371,221 +2365,236 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Job gross margin, December · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B43" s="8">
+      <c r="B44" s="9">
         <f>Workings!B115</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (January)</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each maintenance contract, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B47" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C47" s="11">
-        <f>Workings!B128</f>
-        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B48" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C48" s="11">
-        <f>Workings!B141</f>
+          <t>Wynnum medical centre</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>Workings!B129</f>
+        <v/>
+      </c>
+      <c r="C48" s="12">
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>Workings!B154</f>
+          <t>Ashgrove aged care</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>Workings!B142</f>
+        <v/>
+      </c>
+      <c r="C49" s="12">
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B50" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C50" s="11">
-        <f>Workings!B167</f>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>Workings!B155</f>
+        <v/>
+      </c>
+      <c r="C50" s="12">
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C51" s="11">
-        <f>Workings!B180</f>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B51" s="9">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C51" s="12">
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C52" s="11">
-        <f>Workings!B193</f>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B52" s="9">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C52" s="12">
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C53" s="11">
-        <f>Workings!B206</f>
+          <t>Southbank cafe group</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C53" s="12">
+        <f>Workings!B193</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
-        </is>
-      </c>
-      <c r="B54" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C54" s="11">
-        <f>Workings!B219</f>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B54" s="9">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C54" s="12">
+        <f>Workings!B206</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B55" s="8">
-        <f>Workings!B233</f>
-        <v/>
-      </c>
-      <c r="C55" s="11">
-        <f>Workings!B232</f>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B55" s="9">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C55" s="12">
+        <f>Workings!B219</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>West End brewery</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B246</f>
-        <v/>
-      </c>
-      <c r="C56" s="11">
-        <f>Workings!B245</f>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B56" s="9">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>Workings!B232</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>Workings!B259</f>
-        <v/>
-      </c>
-      <c r="C57" s="11">
-        <f>Workings!B258</f>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C57" s="12">
+        <f>Workings!B245</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B58" s="8">
+      <c r="B59" s="9">
         <f>Workings!B272</f>
         <v/>
       </c>
-      <c r="C58" s="11">
+      <c r="C59" s="12">
         <f>Workings!B271</f>
         <v/>
       </c>
     </row>
-    <row r="59"/>
     <row r="60"/>
     <row r="61"/>
     <row r="62"/>
@@ -2595,87 +2604,72 @@
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>All 12 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in January). All maintenance contracts: 63.8% gross margin, 28.8 points over the 35.0% target ($11,549 ahead on $40,100 in January).</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Installations</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Job gross margin, December · Installations</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>Workings!B290</f>
-        <v/>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
+          <t>Job gross margin, January · Installations</t>
+        </is>
+      </c>
+      <c r="B78" s="9">
+        <f>Workings!B281</f>
+        <v/>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2684,203 +2678,203 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Job gross margin, December · Installations</t>
+        </is>
+      </c>
+      <c r="B79" s="9">
+        <f>Workings!C290</f>
+        <v/>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B79" s="8">
+      <c r="B80" s="9">
         <f>Workings!B306</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (January)</t>
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each installation invoiced in January 2026</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr"/>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Chermside shop data cabling</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>Workings!B320</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B319</f>
-        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Wynnum office data cabling</t>
-        </is>
-      </c>
-      <c r="B84" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B332</f>
+          <t>Chermside shop data cabling</t>
+        </is>
+      </c>
+      <c r="B84" s="9">
+        <f>Workings!B320</f>
+        <v/>
+      </c>
+      <c r="C84" s="12">
+        <f>Workings!B319</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Milton townhouses switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B345</f>
+          <t>Wynnum office data cabling</t>
+        </is>
+      </c>
+      <c r="B85" s="9">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C85" s="12">
+        <f>Workings!B332</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>West End factory switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B86" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B358</f>
+          <t>Milton townhouses switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B86" s="9">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C86" s="12">
+        <f>Workings!B345</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>West End factory switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C87" s="12">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>Mount Gravatt clinic solar and battery</t>
         </is>
       </c>
-      <c r="B87" s="8">
+      <c r="B88" s="9">
         <f>Workings!B372</f>
         <v/>
       </c>
-      <c r="C87" s="11">
+      <c r="C88" s="12">
         <f>Workings!B371</f>
         <v/>
       </c>
     </row>
-    <row r="88"/>
     <row r="89"/>
     <row r="90"/>
     <row r="91"/>
     <row r="92"/>
     <row r="93"/>
     <row r="94"/>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>3 of the 5 installation jobs invoiced in January made less than the 35.0% job gross margin target. The Mount Gravatt clinic solar and battery made a 19.6% job gross margin: 110.0 h of technician time ($7,480) and $3,000 of subcontractors on a $30,200 job. Jobs need 44.2% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>3 installations under the 35.0% target, worth about $5,859 between them on $75,900 of revenue. The biggest gap, Mount Gravatt clinic solar and battery: 19.6% gross margin, 15.4 points under the 35.0% target: about $4,650 on $30,200 of revenue in January. It's below the 44.2% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B103" s="8">
-        <f>Workings!B381</f>
-        <v/>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Job gross margin, December · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B104" s="8">
-        <f>Workings!B390</f>
-        <v/>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
+          <t>Job gross margin, January · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B104" s="9">
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2889,163 +2883,178 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B105" s="8">
-        <f>Workings!B406</f>
-        <v/>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (January)</t>
+          <t>Job gross margin, December · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B105" s="9">
+        <f>Workings!C390</f>
+        <v/>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technician time charged, January</t>
-        </is>
-      </c>
-      <c r="B106" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>69.8% of call-out revenue</t>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B106" s="9">
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (January)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Technician time charged, January</t>
+        </is>
+      </c>
+      <c r="B107" s="12">
+        <f>Workings!B413</f>
+        <v/>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>69.8% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>Materials charged, January</t>
         </is>
       </c>
-      <c r="B107" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="B108" s="12">
+        <f>Workings!B429</f>
+        <v/>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>$7,930 at cost, plus 30%</t>
         </is>
       </c>
     </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr"/>
-      <c r="B110" s="7" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr"/>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (7)</t>
-        </is>
-      </c>
-      <c r="B111" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C111" s="11">
-        <f>Workings!B443</f>
-        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (11)</t>
-        </is>
-      </c>
-      <c r="B112" s="8">
-        <f>Workings!B457</f>
-        <v/>
-      </c>
-      <c r="C112" s="11">
-        <f>Workings!B456</f>
+          <t>1-hour call-outs (7)</t>
+        </is>
+      </c>
+      <c r="B112" s="9">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C112" s="12">
+        <f>Workings!B443</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2-hour call-outs (8)</t>
-        </is>
-      </c>
-      <c r="B113" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C113" s="11">
-        <f>Workings!B469</f>
+          <t>1.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B113" s="9">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C113" s="12">
+        <f>Workings!B456</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (11)</t>
-        </is>
-      </c>
-      <c r="B114" s="8">
-        <f>Workings!B483</f>
-        <v/>
-      </c>
-      <c r="C114" s="11">
-        <f>Workings!B482</f>
+          <t>2-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B114" s="9">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C114" s="12">
+        <f>Workings!B469</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3-hour call-outs (21)</t>
-        </is>
-      </c>
-      <c r="B115" s="8">
-        <f>Workings!B496</f>
-        <v/>
-      </c>
-      <c r="C115" s="11">
-        <f>Workings!B495</f>
+          <t>2.5-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B115" s="9">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>Workings!B482</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>3-hour call-outs (21)</t>
+        </is>
+      </c>
+      <c r="B116" s="9">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>4-hour call-outs (4)</t>
         </is>
       </c>
-      <c r="B116" s="8">
+      <c r="B117" s="9">
         <f>Workings!B509</f>
         <v/>
       </c>
-      <c r="C116" s="11">
+      <c r="C117" s="12">
         <f>Workings!B508</f>
         <v/>
       </c>
     </row>
-    <row r="117"/>
     <row r="118"/>
     <row r="119"/>
     <row r="120"/>
@@ -3053,83 +3062,85 @@
     <row r="122"/>
     <row r="123"/>
     <row r="124"/>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>62 call-outs in January billed $23,797 of technician time and $10,309 of materials ($7,930 at cost plus 30%), and made a 47.6% job gross margin between them. Gross margins run from 40.7% to 50.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="30" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>All call-outs: 47.6% gross margin, 12.6 points over the 35.0% target ($4,311 ahead on $34,106 in January).</t>
         </is>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="12" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="133"/>
     <row r="134"/>
+    <row r="135"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="5" manualBreakCount="5">
-    <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="68" min="0" max="16383" man="1"/>
-    <brk id="94" min="0" max="16383" man="1"/>
-    <brk id="108" min="0" max="16383" man="1"/>
+    <brk id="19" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="69" min="0" max="16383" man="1"/>
+    <brk id="95" min="0" max="16383" man="1"/>
+    <brk id="109" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3167,28 +3178,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -3200,7 +3211,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>76716</v>
       </c>
     </row>
@@ -3210,7 +3221,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3220,7 +3231,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>49980</v>
       </c>
     </row>
@@ -3230,7 +3241,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -3241,7 +3252,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>B8-B11</f>
         <v/>
       </c>
@@ -3252,7 +3263,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>58730</v>
       </c>
     </row>
@@ -3262,7 +3273,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>B12-B13</f>
         <v/>
       </c>
@@ -3273,7 +3284,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -3283,7 +3294,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B8/B15</f>
         <v/>
       </c>
@@ -3294,18 +3305,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <f>(B11+B13)/B15</f>
         <v/>
       </c>
@@ -3320,27 +3331,27 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -3352,10 +3363,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>183306</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>150283</v>
       </c>
     </row>
@@ -3365,10 +3376,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>106590</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>84626</v>
       </c>
     </row>
@@ -3378,26 +3389,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <f>B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <f>C25-C26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/B25</f>
         <v/>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <f>C27/C25</f>
         <v/>
       </c>
@@ -3405,27 +3416,27 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -3437,10 +3448,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="n">
         <v>183306</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <v>150283</v>
       </c>
     </row>
@@ -3450,10 +3461,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>106590</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>84626</v>
       </c>
     </row>
@@ -3463,26 +3474,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>C34-C35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <f>B36/B34</f>
         <v/>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <f>C36/C34</f>
         <v/>
       </c>
@@ -3490,22 +3501,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -3517,7 +3528,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>76716</v>
       </c>
     </row>
@@ -3527,7 +3538,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3537,7 +3548,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>49980</v>
       </c>
     </row>
@@ -3547,7 +3558,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>B44-B45</f>
         <v/>
       </c>
@@ -3558,7 +3569,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <f>B43-B46</f>
         <v/>
       </c>
@@ -3569,7 +3580,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>58730</v>
       </c>
     </row>
@@ -3579,7 +3590,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47-B48</f>
         <v/>
       </c>
@@ -3590,7 +3601,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="B50" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -3600,7 +3611,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <f>B43/B50</f>
         <v/>
       </c>
@@ -3611,18 +3622,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <f>B49/B50</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <f>(B46+B48)/B50</f>
         <v/>
       </c>
@@ -3637,22 +3648,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Maintenance contracts, January</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -3664,7 +3675,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3674,7 +3685,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3684,18 +3695,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60-B61</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <f>B62/B60</f>
         <v/>
       </c>
@@ -3703,22 +3714,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Installations, January</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -3730,7 +3741,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B69" s="13" t="n">
+      <c r="B69" s="14" t="n">
         <v>109100</v>
       </c>
     </row>
@@ -3740,7 +3751,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B70" s="13" t="n">
+      <c r="B70" s="14" t="n">
         <v>74216</v>
       </c>
     </row>
@@ -3750,18 +3761,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <f>B69-B70</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <f>B71/B69</f>
         <v/>
       </c>
@@ -3769,22 +3780,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Call-outs and repairs, January</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -3796,7 +3807,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B78" s="13" t="n">
+      <c r="B78" s="14" t="n">
         <v>34106</v>
       </c>
     </row>
@@ -3806,7 +3817,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n">
+      <c r="B79" s="14" t="n">
         <v>17858</v>
       </c>
     </row>
@@ -3816,18 +3827,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="14">
         <f>B78-B79</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <f>B80/B78</f>
         <v/>
       </c>
@@ -3835,27 +3846,27 @@
     <row r="82"/>
     <row r="83"/>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -3867,10 +3878,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B87" s="13" t="n">
+      <c r="B87" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3880,10 +3891,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B88" s="13" t="n">
+      <c r="B88" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3893,26 +3904,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="14">
         <f>B87-B88</f>
         <v/>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="14">
         <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <f>B89/B87</f>
         <v/>
       </c>
-      <c r="C90" s="16">
+      <c r="C90" s="17">
         <f>C89/C87</f>
         <v/>
       </c>
@@ -3920,27 +3931,27 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -3952,10 +3963,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B96" s="13" t="n">
+      <c r="B96" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="C96" s="13" t="n">
+      <c r="C96" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3965,10 +3976,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B97" s="13" t="n">
+      <c r="B97" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3978,26 +3989,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="14">
         <f>B96-B97</f>
         <v/>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="14">
         <f>C96-C97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <f>B98/B96</f>
         <v/>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="17">
         <f>C98/C96</f>
         <v/>
       </c>
@@ -4005,22 +4016,22 @@
     <row r="100"/>
     <row r="101"/>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr"/>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4032,7 +4043,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B105" s="13" t="n">
+      <c r="B105" s="14" t="n">
         <v>76716</v>
       </c>
     </row>
@@ -4042,7 +4053,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B106" s="13" t="n">
+      <c r="B106" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -4052,7 +4063,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B107" s="13" t="n">
+      <c r="B107" s="14" t="n">
         <v>49980</v>
       </c>
     </row>
@@ -4062,7 +4073,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="14">
         <f>B106-B107</f>
         <v/>
       </c>
@@ -4073,7 +4084,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="14">
         <f>B105-B108</f>
         <v/>
       </c>
@@ -4084,7 +4095,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B110" s="13" t="n">
+      <c r="B110" s="14" t="n">
         <v>58730</v>
       </c>
     </row>
@@ -4094,7 +4105,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="14">
         <f>B109-B110</f>
         <v/>
       </c>
@@ -4105,7 +4116,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B112" s="13" t="n">
+      <c r="B112" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -4115,7 +4126,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B113" s="14">
+      <c r="B113" s="15">
         <f>B105/B112</f>
         <v/>
       </c>
@@ -4126,18 +4137,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B114" s="14">
+      <c r="B114" s="15">
         <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <f>(B108+B110)/B112</f>
         <v/>
       </c>
@@ -4152,22 +4163,22 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="12" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr"/>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4179,7 +4190,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B122" s="13" t="n">
+      <c r="B122" s="14" t="n">
         <v>2450</v>
       </c>
     </row>
@@ -4189,7 +4200,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B123" s="13" t="n">
+      <c r="B123" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4199,7 +4210,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B124" s="13" t="n">
+      <c r="B124" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4209,7 +4220,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B125" s="17" t="n">
+      <c r="B125" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4219,7 +4230,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B126" s="13" t="n">
+      <c r="B126" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4229,7 +4240,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="14">
         <f>-B125*B126</f>
         <v/>
       </c>
@@ -4240,18 +4251,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="14">
         <f>B122+B123+B124+B127</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <f>B128/B122</f>
         <v/>
       </c>
@@ -4259,22 +4270,22 @@
     <row r="130"/>
     <row r="131"/>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="12" t="inlineStr">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr"/>
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4286,7 +4297,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B135" s="13" t="n">
+      <c r="B135" s="14" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -4296,7 +4307,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B136" s="13" t="n">
+      <c r="B136" s="14" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -4306,7 +4317,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B137" s="13" t="n">
+      <c r="B137" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4316,7 +4327,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B138" s="17" t="n">
+      <c r="B138" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4326,7 +4337,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B139" s="13" t="n">
+      <c r="B139" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4336,7 +4347,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="14">
         <f>-B138*B139</f>
         <v/>
       </c>
@@ -4347,18 +4358,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="14">
         <f>B135+B136+B137+B140</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <f>B141/B135</f>
         <v/>
       </c>
@@ -4366,22 +4377,22 @@
     <row r="143"/>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr"/>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4393,7 +4404,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B148" s="13" t="n">
+      <c r="B148" s="14" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -4403,7 +4414,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B149" s="13" t="n">
+      <c r="B149" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4413,7 +4424,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n">
+      <c r="B150" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4423,7 +4434,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B151" s="17" t="n">
+      <c r="B151" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4433,7 +4444,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B152" s="13" t="n">
+      <c r="B152" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4443,7 +4454,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="14">
         <f>-B151*B152</f>
         <v/>
       </c>
@@ -4454,18 +4465,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="14">
         <f>B148+B149+B150+B153</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="15" t="inlineStr">
+      <c r="A155" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <f>B154/B148</f>
         <v/>
       </c>
@@ -4473,22 +4484,22 @@
     <row r="156"/>
     <row r="157"/>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr"/>
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4500,7 +4511,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B161" s="13" t="n">
+      <c r="B161" s="14" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -4510,7 +4521,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B162" s="13" t="n">
+      <c r="B162" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4520,7 +4531,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B163" s="13" t="n">
+      <c r="B163" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4530,7 +4541,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B164" s="17" t="n">
+      <c r="B164" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4540,7 +4551,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B165" s="13" t="n">
+      <c r="B165" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4550,7 +4561,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="14">
         <f>-B164*B165</f>
         <v/>
       </c>
@@ -4561,18 +4572,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="14">
         <f>B161+B162+B163+B166</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <f>B167/B161</f>
         <v/>
       </c>
@@ -4580,22 +4591,22 @@
     <row r="169"/>
     <row r="170"/>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="inlineStr">
+      <c r="A172" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr"/>
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4607,7 +4618,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B174" s="13" t="n">
+      <c r="B174" s="14" t="n">
         <v>3800</v>
       </c>
     </row>
@@ -4617,7 +4628,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B175" s="13" t="n">
+      <c r="B175" s="14" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -4627,7 +4638,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B176" s="13" t="n">
+      <c r="B176" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4637,7 +4648,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B177" s="17" t="n">
+      <c r="B177" s="18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4647,7 +4658,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B178" s="13" t="n">
+      <c r="B178" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4657,7 +4668,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="14">
         <f>-B177*B178</f>
         <v/>
       </c>
@@ -4668,18 +4679,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="14">
         <f>B174+B175+B176+B179</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="15" t="inlineStr">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <f>B180/B174</f>
         <v/>
       </c>
@@ -4687,22 +4698,22 @@
     <row r="182"/>
     <row r="183"/>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr"/>
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4714,7 +4725,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B187" s="13" t="n">
+      <c r="B187" s="14" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -4724,7 +4735,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B188" s="13" t="n">
+      <c r="B188" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4734,7 +4745,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B189" s="13" t="n">
+      <c r="B189" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4744,7 +4755,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B190" s="17" t="n">
+      <c r="B190" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4754,7 +4765,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B191" s="13" t="n">
+      <c r="B191" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4764,7 +4775,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="14">
         <f>-B190*B191</f>
         <v/>
       </c>
@@ -4775,18 +4786,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="14">
         <f>B187+B188+B189+B192</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
+      <c r="A194" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <f>B193/B187</f>
         <v/>
       </c>
@@ -4794,22 +4805,22 @@
     <row r="195"/>
     <row r="196"/>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="inlineStr">
+      <c r="A198" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr"/>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="A199" s="7" t="inlineStr"/>
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4821,7 +4832,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B200" s="13" t="n">
+      <c r="B200" s="14" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -4831,7 +4842,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B201" s="13" t="n">
+      <c r="B201" s="14" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4841,7 +4852,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B202" s="13" t="n">
+      <c r="B202" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4851,7 +4862,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B203" s="17" t="n">
+      <c r="B203" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4861,7 +4872,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B204" s="13" t="n">
+      <c r="B204" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4871,7 +4882,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="14">
         <f>-B203*B204</f>
         <v/>
       </c>
@@ -4882,18 +4893,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="14">
         <f>B200+B201+B202+B205</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="15" t="inlineStr">
+      <c r="A207" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <f>B206/B200</f>
         <v/>
       </c>
@@ -4901,22 +4912,22 @@
     <row r="208"/>
     <row r="209"/>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="12" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr"/>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="A212" s="7" t="inlineStr"/>
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4928,7 +4939,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B213" s="13" t="n">
+      <c r="B213" s="14" t="n">
         <v>3150</v>
       </c>
     </row>
@@ -4938,7 +4949,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B214" s="13" t="n">
+      <c r="B214" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4948,7 +4959,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B215" s="13" t="n">
+      <c r="B215" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4958,7 +4969,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B216" s="17" t="n">
+      <c r="B216" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4968,7 +4979,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B217" s="13" t="n">
+      <c r="B217" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4978,7 +4989,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="14">
         <f>-B216*B217</f>
         <v/>
       </c>
@@ -4989,18 +5000,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="14">
         <f>B213+B214+B215+B218</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <f>B219/B213</f>
         <v/>
       </c>
@@ -5008,22 +5019,22 @@
     <row r="221"/>
     <row r="222"/>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="12" t="inlineStr">
+      <c r="A224" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="A225" s="7" t="inlineStr"/>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5035,7 +5046,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B226" s="13" t="n">
+      <c r="B226" s="14" t="n">
         <v>4700</v>
       </c>
     </row>
@@ -5045,7 +5056,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B227" s="13" t="n">
+      <c r="B227" s="14" t="n">
         <v>-90</v>
       </c>
     </row>
@@ -5055,7 +5066,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B228" s="13" t="n">
+      <c r="B228" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5065,7 +5076,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B229" s="17" t="n">
+      <c r="B229" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5075,7 +5086,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B230" s="13" t="n">
+      <c r="B230" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5085,7 +5096,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="14">
         <f>-B229*B230</f>
         <v/>
       </c>
@@ -5096,18 +5107,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="14">
         <f>B226+B227+B228+B231</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="15" t="inlineStr">
+      <c r="A233" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <f>B232/B226</f>
         <v/>
       </c>
@@ -5115,22 +5126,22 @@
     <row r="234"/>
     <row r="235"/>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="12" t="inlineStr">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr"/>
-      <c r="B238" s="7" t="inlineStr">
+      <c r="A238" s="7" t="inlineStr"/>
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5142,7 +5153,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B239" s="13" t="n">
+      <c r="B239" s="14" t="n">
         <v>2900</v>
       </c>
     </row>
@@ -5152,7 +5163,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B240" s="13" t="n">
+      <c r="B240" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5162,7 +5173,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B241" s="13" t="n">
+      <c r="B241" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5172,7 +5183,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B242" s="17" t="n">
+      <c r="B242" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5182,7 +5193,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B243" s="13" t="n">
+      <c r="B243" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5192,7 +5203,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B244" s="13">
+      <c r="B244" s="14">
         <f>-B242*B243</f>
         <v/>
       </c>
@@ -5203,18 +5214,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B245" s="13">
+      <c r="B245" s="14">
         <f>B239+B240+B241+B244</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr">
+      <c r="A246" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <f>B245/B239</f>
         <v/>
       </c>
@@ -5222,22 +5233,22 @@
     <row r="247"/>
     <row r="248"/>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="12" t="inlineStr">
+      <c r="A250" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr"/>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr"/>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5249,7 +5260,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B252" s="13" t="n">
+      <c r="B252" s="14" t="n">
         <v>4350</v>
       </c>
     </row>
@@ -5259,7 +5270,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B253" s="13" t="n">
+      <c r="B253" s="14" t="n">
         <v>-110</v>
       </c>
     </row>
@@ -5269,7 +5280,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B254" s="13" t="n">
+      <c r="B254" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5279,7 +5290,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B255" s="17" t="n">
+      <c r="B255" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5289,7 +5300,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B256" s="13" t="n">
+      <c r="B256" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5299,7 +5310,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B257" s="13">
+      <c r="B257" s="14">
         <f>-B255*B256</f>
         <v/>
       </c>
@@ -5310,18 +5321,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B258" s="13">
+      <c r="B258" s="14">
         <f>B252+B253+B254+B257</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="15" t="inlineStr">
+      <c r="A259" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <f>B258/B252</f>
         <v/>
       </c>
@@ -5329,22 +5340,22 @@
     <row r="260"/>
     <row r="261"/>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="A263" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr"/>
-      <c r="B264" s="7" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr"/>
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5356,7 +5367,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B265" s="13" t="n">
+      <c r="B265" s="14" t="n">
         <v>2700</v>
       </c>
     </row>
@@ -5366,7 +5377,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B266" s="13" t="n">
+      <c r="B266" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5376,7 +5387,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B267" s="13" t="n">
+      <c r="B267" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5386,7 +5397,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B268" s="17" t="n">
+      <c r="B268" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5396,7 +5407,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B269" s="13" t="n">
+      <c r="B269" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5406,7 +5417,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B270" s="13">
+      <c r="B270" s="14">
         <f>-B268*B269</f>
         <v/>
       </c>
@@ -5417,18 +5428,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B271" s="13">
+      <c r="B271" s="14">
         <f>B265+B266+B267+B270</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr">
+      <c r="A272" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <f>B271/B265</f>
         <v/>
       </c>
@@ -5436,27 +5447,27 @@
     <row r="273"/>
     <row r="274"/>
     <row r="275">
-      <c r="A275" s="5" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="12" t="inlineStr">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr"/>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="A277" s="7" t="inlineStr"/>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C277" s="7" t="inlineStr">
+      <c r="C277" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -5468,10 +5479,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B278" s="13" t="n">
+      <c r="B278" s="14" t="n">
         <v>109100</v>
       </c>
-      <c r="C278" s="13" t="n">
+      <c r="C278" s="14" t="n">
         <v>78100</v>
       </c>
     </row>
@@ -5481,10 +5492,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B279" s="13" t="n">
+      <c r="B279" s="14" t="n">
         <v>74216</v>
       </c>
-      <c r="C279" s="13" t="n">
+      <c r="C279" s="14" t="n">
         <v>53408</v>
       </c>
     </row>
@@ -5494,26 +5505,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B280" s="13">
+      <c r="B280" s="14">
         <f>B278-B279</f>
         <v/>
       </c>
-      <c r="C280" s="13">
+      <c r="C280" s="14">
         <f>C278-C279</f>
         <v/>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="15" t="inlineStr">
+      <c r="A281" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B281" s="16">
+      <c r="B281" s="17">
         <f>B280/B278</f>
         <v/>
       </c>
-      <c r="C281" s="16">
+      <c r="C281" s="17">
         <f>C280/C278</f>
         <v/>
       </c>
@@ -5521,27 +5532,27 @@
     <row r="282"/>
     <row r="283"/>
     <row r="284">
-      <c r="A284" s="5" t="inlineStr">
+      <c r="A284" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="12" t="inlineStr">
+      <c r="A285" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
+      <c r="A286" s="7" t="inlineStr"/>
+      <c r="B286" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C286" s="7" t="inlineStr">
+      <c r="C286" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -5553,10 +5564,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B287" s="13" t="n">
+      <c r="B287" s="14" t="n">
         <v>109100</v>
       </c>
-      <c r="C287" s="13" t="n">
+      <c r="C287" s="14" t="n">
         <v>78100</v>
       </c>
     </row>
@@ -5566,10 +5577,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B288" s="13" t="n">
+      <c r="B288" s="14" t="n">
         <v>74216</v>
       </c>
-      <c r="C288" s="13" t="n">
+      <c r="C288" s="14" t="n">
         <v>53408</v>
       </c>
     </row>
@@ -5579,26 +5590,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B289" s="13">
+      <c r="B289" s="14">
         <f>B287-B288</f>
         <v/>
       </c>
-      <c r="C289" s="13">
+      <c r="C289" s="14">
         <f>C287-C288</f>
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="15" t="inlineStr">
+      <c r="A290" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B290" s="16">
+      <c r="B290" s="17">
         <f>B289/B287</f>
         <v/>
       </c>
-      <c r="C290" s="16">
+      <c r="C290" s="17">
         <f>C289/C287</f>
         <v/>
       </c>
@@ -5606,22 +5617,22 @@
     <row r="291"/>
     <row r="292"/>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="12" t="inlineStr">
+      <c r="A294" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr"/>
-      <c r="B295" s="7" t="inlineStr">
+      <c r="A295" s="7" t="inlineStr"/>
+      <c r="B295" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5633,7 +5644,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B296" s="13" t="n">
+      <c r="B296" s="14" t="n">
         <v>76716</v>
       </c>
     </row>
@@ -5643,7 +5654,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B297" s="13" t="n">
+      <c r="B297" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -5653,7 +5664,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B298" s="13" t="n">
+      <c r="B298" s="14" t="n">
         <v>49980</v>
       </c>
     </row>
@@ -5663,7 +5674,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B299" s="13">
+      <c r="B299" s="14">
         <f>B297-B298</f>
         <v/>
       </c>
@@ -5674,7 +5685,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B300" s="13">
+      <c r="B300" s="14">
         <f>B296-B299</f>
         <v/>
       </c>
@@ -5685,7 +5696,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B301" s="13" t="n">
+      <c r="B301" s="14" t="n">
         <v>58730</v>
       </c>
     </row>
@@ -5695,7 +5706,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B302" s="13">
+      <c r="B302" s="14">
         <f>B300-B301</f>
         <v/>
       </c>
@@ -5706,7 +5717,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B303" s="13" t="n">
+      <c r="B303" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -5716,7 +5727,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B304" s="14">
+      <c r="B304" s="15">
         <f>B296/B303</f>
         <v/>
       </c>
@@ -5727,18 +5738,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B305" s="14">
+      <c r="B305" s="15">
         <f>B302/B303</f>
         <v/>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="15" t="inlineStr">
+      <c r="A306" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B306" s="16">
+      <c r="B306" s="17">
         <f>(B299+B301)/B303</f>
         <v/>
       </c>
@@ -5753,22 +5764,22 @@
     <row r="308"/>
     <row r="309"/>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
+      <c r="A310" s="6" t="inlineStr">
         <is>
           <t>Chermside shop data cabling</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="12" t="inlineStr">
+      <c r="A311" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="inlineStr"/>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="A312" s="7" t="inlineStr"/>
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5780,7 +5791,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B313" s="13" t="n">
+      <c r="B313" s="14" t="n">
         <v>20900</v>
       </c>
     </row>
@@ -5790,7 +5801,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B314" s="13" t="n">
+      <c r="B314" s="14" t="n">
         <v>-4300</v>
       </c>
     </row>
@@ -5800,7 +5811,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B315" s="13" t="n">
+      <c r="B315" s="14" t="n">
         <v>-2200</v>
       </c>
     </row>
@@ -5810,7 +5821,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B316" s="17" t="n">
+      <c r="B316" s="18" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -5820,7 +5831,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B317" s="13" t="n">
+      <c r="B317" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5830,7 +5841,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B318" s="13">
+      <c r="B318" s="14">
         <f>-B316*B317</f>
         <v/>
       </c>
@@ -5841,18 +5852,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B319" s="13">
+      <c r="B319" s="14">
         <f>B313+B314+B315+B318</f>
         <v/>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="15" t="inlineStr">
+      <c r="A320" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B320" s="16">
+      <c r="B320" s="17">
         <f>B319/B313</f>
         <v/>
       </c>
@@ -5860,22 +5871,22 @@
     <row r="321"/>
     <row r="322"/>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>Wynnum office data cabling</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="12" t="inlineStr">
+      <c r="A324" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr"/>
-      <c r="B325" s="7" t="inlineStr">
+      <c r="A325" s="7" t="inlineStr"/>
+      <c r="B325" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5887,7 +5898,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B326" s="13" t="n">
+      <c r="B326" s="14" t="n">
         <v>12300</v>
       </c>
     </row>
@@ -5897,7 +5908,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B327" s="13" t="n">
+      <c r="B327" s="14" t="n">
         <v>-3300</v>
       </c>
     </row>
@@ -5907,7 +5918,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B328" s="13" t="n">
+      <c r="B328" s="14" t="n">
         <v>-1300</v>
       </c>
     </row>
@@ -5917,7 +5928,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B329" s="17" t="n">
+      <c r="B329" s="18" t="n">
         <v>44</v>
       </c>
     </row>
@@ -5927,7 +5938,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B330" s="13" t="n">
+      <c r="B330" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5937,7 +5948,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B331" s="13">
+      <c r="B331" s="14">
         <f>-B329*B330</f>
         <v/>
       </c>
@@ -5948,18 +5959,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B332" s="13">
+      <c r="B332" s="14">
         <f>B326+B327+B328+B331</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="15" t="inlineStr">
+      <c r="A333" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B333" s="16">
+      <c r="B333" s="17">
         <f>B332/B326</f>
         <v/>
       </c>
@@ -5967,22 +5978,22 @@
     <row r="334"/>
     <row r="335"/>
     <row r="336">
-      <c r="A336" s="5" t="inlineStr">
+      <c r="A336" s="6" t="inlineStr">
         <is>
           <t>Milton townhouses switchboard upgrade</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="12" t="inlineStr">
+      <c r="A337" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="6" t="inlineStr"/>
-      <c r="B338" s="7" t="inlineStr">
+      <c r="A338" s="7" t="inlineStr"/>
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5994,7 +6005,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B339" s="13" t="n">
+      <c r="B339" s="14" t="n">
         <v>14700</v>
       </c>
     </row>
@@ -6004,7 +6015,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B340" s="13" t="n">
+      <c r="B340" s="14" t="n">
         <v>-5200</v>
       </c>
     </row>
@@ -6014,7 +6025,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B341" s="13" t="n">
+      <c r="B341" s="14" t="n">
         <v>-1300</v>
       </c>
     </row>
@@ -6024,7 +6035,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B342" s="17" t="n">
+      <c r="B342" s="18" t="n">
         <v>49.5</v>
       </c>
     </row>
@@ -6034,7 +6045,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B343" s="13" t="n">
+      <c r="B343" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6044,7 +6055,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B344" s="13">
+      <c r="B344" s="14">
         <f>-B342*B343</f>
         <v/>
       </c>
@@ -6055,18 +6066,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B345" s="13">
+      <c r="B345" s="14">
         <f>B339+B340+B341+B344</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="15" t="inlineStr">
+      <c r="A346" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B346" s="16">
+      <c r="B346" s="17">
         <f>B345/B339</f>
         <v/>
       </c>
@@ -6074,22 +6085,22 @@
     <row r="347"/>
     <row r="348"/>
     <row r="349">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>West End factory switchboard upgrade</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="12" t="inlineStr">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="6" t="inlineStr"/>
-      <c r="B351" s="7" t="inlineStr">
+      <c r="A351" s="7" t="inlineStr"/>
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6101,7 +6112,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B352" s="13" t="n">
+      <c r="B352" s="14" t="n">
         <v>31000</v>
       </c>
     </row>
@@ -6111,7 +6122,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
+      <c r="B353" s="14" t="n">
         <v>-10700</v>
       </c>
     </row>
@@ -6121,7 +6132,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B354" s="13" t="n">
+      <c r="B354" s="14" t="n">
         <v>-2800</v>
       </c>
     </row>
@@ -6131,7 +6142,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B355" s="17" t="n">
+      <c r="B355" s="18" t="n">
         <v>111</v>
       </c>
     </row>
@@ -6141,7 +6152,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B356" s="13" t="n">
+      <c r="B356" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6151,7 +6162,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B357" s="13">
+      <c r="B357" s="14">
         <f>-B355*B356</f>
         <v/>
       </c>
@@ -6162,18 +6173,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B358" s="13">
+      <c r="B358" s="14">
         <f>B352+B353+B354+B357</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="15" t="inlineStr">
+      <c r="A359" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B359" s="16">
+      <c r="B359" s="17">
         <f>B358/B352</f>
         <v/>
       </c>
@@ -6181,22 +6192,22 @@
     <row r="360"/>
     <row r="361"/>
     <row r="362">
-      <c r="A362" s="5" t="inlineStr">
+      <c r="A362" s="6" t="inlineStr">
         <is>
           <t>Mount Gravatt clinic solar and battery</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="12" t="inlineStr">
+      <c r="A363" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="6" t="inlineStr"/>
-      <c r="B364" s="7" t="inlineStr">
+      <c r="A364" s="7" t="inlineStr"/>
+      <c r="B364" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6208,7 +6219,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B365" s="13" t="n">
+      <c r="B365" s="14" t="n">
         <v>30200</v>
       </c>
     </row>
@@ -6218,7 +6229,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B366" s="13" t="n">
+      <c r="B366" s="14" t="n">
         <v>-13800</v>
       </c>
     </row>
@@ -6228,7 +6239,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
+      <c r="B367" s="14" t="n">
         <v>-3000</v>
       </c>
     </row>
@@ -6238,7 +6249,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B368" s="17" t="n">
+      <c r="B368" s="18" t="n">
         <v>110</v>
       </c>
     </row>
@@ -6248,7 +6259,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B369" s="13" t="n">
+      <c r="B369" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6258,7 +6269,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B370" s="13">
+      <c r="B370" s="14">
         <f>-B368*B369</f>
         <v/>
       </c>
@@ -6269,18 +6280,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B371" s="13">
+      <c r="B371" s="14">
         <f>B365+B366+B367+B370</f>
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="15" t="inlineStr">
+      <c r="A372" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B372" s="16">
+      <c r="B372" s="17">
         <f>B371/B365</f>
         <v/>
       </c>
@@ -6288,27 +6299,27 @@
     <row r="373"/>
     <row r="374"/>
     <row r="375">
-      <c r="A375" s="5" t="inlineStr">
+      <c r="A375" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="12" t="inlineStr">
+      <c r="A376" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="6" t="inlineStr"/>
-      <c r="B377" s="7" t="inlineStr">
+      <c r="A377" s="7" t="inlineStr"/>
+      <c r="B377" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C377" s="7" t="inlineStr">
+      <c r="C377" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -6320,10 +6331,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B378" s="13" t="n">
+      <c r="B378" s="14" t="n">
         <v>34106</v>
       </c>
-      <c r="C378" s="13" t="n">
+      <c r="C378" s="14" t="n">
         <v>32083</v>
       </c>
     </row>
@@ -6333,10 +6344,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B379" s="13" t="n">
+      <c r="B379" s="14" t="n">
         <v>17858</v>
       </c>
-      <c r="C379" s="13" t="n">
+      <c r="C379" s="14" t="n">
         <v>16702</v>
       </c>
     </row>
@@ -6346,26 +6357,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B380" s="13">
+      <c r="B380" s="14">
         <f>B378-B379</f>
         <v/>
       </c>
-      <c r="C380" s="13">
+      <c r="C380" s="14">
         <f>C378-C379</f>
         <v/>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="15" t="inlineStr">
+      <c r="A381" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B381" s="16">
+      <c r="B381" s="17">
         <f>B380/B378</f>
         <v/>
       </c>
-      <c r="C381" s="16">
+      <c r="C381" s="17">
         <f>C380/C378</f>
         <v/>
       </c>
@@ -6373,27 +6384,27 @@
     <row r="382"/>
     <row r="383"/>
     <row r="384">
-      <c r="A384" s="5" t="inlineStr">
+      <c r="A384" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, January and December</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="12" t="inlineStr">
+      <c r="A385" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="6" t="inlineStr"/>
-      <c r="B386" s="7" t="inlineStr">
+      <c r="A386" s="7" t="inlineStr"/>
+      <c r="B386" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C386" s="7" t="inlineStr">
+      <c r="C386" s="8" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -6405,10 +6416,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B387" s="13" t="n">
+      <c r="B387" s="14" t="n">
         <v>34106</v>
       </c>
-      <c r="C387" s="13" t="n">
+      <c r="C387" s="14" t="n">
         <v>32083</v>
       </c>
     </row>
@@ -6418,10 +6429,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B388" s="13" t="n">
+      <c r="B388" s="14" t="n">
         <v>17858</v>
       </c>
-      <c r="C388" s="13" t="n">
+      <c r="C388" s="14" t="n">
         <v>16702</v>
       </c>
     </row>
@@ -6431,26 +6442,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B389" s="13">
+      <c r="B389" s="14">
         <f>B387-B388</f>
         <v/>
       </c>
-      <c r="C389" s="13">
+      <c r="C389" s="14">
         <f>C387-C388</f>
         <v/>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="15" t="inlineStr">
+      <c r="A390" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B390" s="16">
+      <c r="B390" s="17">
         <f>B389/B387</f>
         <v/>
       </c>
-      <c r="C390" s="16">
+      <c r="C390" s="17">
         <f>C389/C387</f>
         <v/>
       </c>
@@ -6458,22 +6469,22 @@
     <row r="391"/>
     <row r="392"/>
     <row r="393">
-      <c r="A393" s="5" t="inlineStr">
+      <c r="A393" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, January 2026</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="12" t="inlineStr">
+      <c r="A394" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="6" t="inlineStr"/>
-      <c r="B395" s="7" t="inlineStr">
+      <c r="A395" s="7" t="inlineStr"/>
+      <c r="B395" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -6485,7 +6496,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B396" s="13" t="n">
+      <c r="B396" s="14" t="n">
         <v>76716</v>
       </c>
     </row>
@@ -6495,7 +6506,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B397" s="13" t="n">
+      <c r="B397" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -6505,7 +6516,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B398" s="13" t="n">
+      <c r="B398" s="14" t="n">
         <v>49980</v>
       </c>
     </row>
@@ -6515,7 +6526,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B399" s="13">
+      <c r="B399" s="14">
         <f>B397-B398</f>
         <v/>
       </c>
@@ -6526,7 +6537,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B400" s="13">
+      <c r="B400" s="14">
         <f>B396-B399</f>
         <v/>
       </c>
@@ -6537,7 +6548,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B401" s="13" t="n">
+      <c r="B401" s="14" t="n">
         <v>58730</v>
       </c>
     </row>
@@ -6547,7 +6558,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B402" s="13">
+      <c r="B402" s="14">
         <f>B400-B401</f>
         <v/>
       </c>
@@ -6558,7 +6569,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B403" s="13" t="n">
+      <c r="B403" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -6568,7 +6579,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B404" s="14">
+      <c r="B404" s="15">
         <f>B396/B403</f>
         <v/>
       </c>
@@ -6579,18 +6590,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B405" s="14">
+      <c r="B405" s="15">
         <f>B402/B403</f>
         <v/>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="15" t="inlineStr">
+      <c r="A406" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B406" s="16">
+      <c r="B406" s="17">
         <f>(B399+B401)/B403</f>
         <v/>
       </c>
@@ -6605,22 +6616,22 @@
     <row r="408"/>
     <row r="409"/>
     <row r="410">
-      <c r="A410" s="5" t="inlineStr">
+      <c r="A410" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, January</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="12" t="inlineStr">
+      <c r="A411" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="6" t="inlineStr"/>
-      <c r="B412" s="7" t="inlineStr">
+      <c r="A412" s="7" t="inlineStr"/>
+      <c r="B412" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -6632,7 +6643,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B413" s="13" t="n">
+      <c r="B413" s="14" t="n">
         <v>23797</v>
       </c>
     </row>
@@ -6642,7 +6653,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B414" s="13" t="n">
+      <c r="B414" s="14" t="n">
         <v>7930</v>
       </c>
     </row>
@@ -6652,7 +6663,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B415" s="14" t="n">
+      <c r="B415" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6662,7 +6673,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B416" s="13">
+      <c r="B416" s="14">
         <f>B414*(1+B415)</f>
         <v/>
       </c>
@@ -6673,7 +6684,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B417" s="13" t="n">
+      <c r="B417" s="14" t="n">
         <v>10309</v>
       </c>
     </row>
@@ -6683,18 +6694,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B418" s="13">
+      <c r="B418" s="14">
         <f>B413+B417</f>
         <v/>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="15" t="inlineStr">
+      <c r="A419" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B419" s="16">
+      <c r="B419" s="17">
         <f>B413/B418</f>
         <v/>
       </c>
@@ -6702,22 +6713,22 @@
     <row r="420"/>
     <row r="421"/>
     <row r="422">
-      <c r="A422" s="5" t="inlineStr">
+      <c r="A422" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, January</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="12" t="inlineStr">
+      <c r="A423" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="6" t="inlineStr"/>
-      <c r="B424" s="7" t="inlineStr">
+      <c r="A424" s="7" t="inlineStr"/>
+      <c r="B424" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -6729,7 +6740,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B425" s="13" t="n">
+      <c r="B425" s="14" t="n">
         <v>23797</v>
       </c>
     </row>
@@ -6739,7 +6750,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B426" s="13" t="n">
+      <c r="B426" s="14" t="n">
         <v>7930</v>
       </c>
     </row>
@@ -6749,7 +6760,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B427" s="14" t="n">
+      <c r="B427" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6759,7 +6770,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B428" s="13">
+      <c r="B428" s="14">
         <f>B426*(1+B427)</f>
         <v/>
       </c>
@@ -6770,7 +6781,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B429" s="13" t="n">
+      <c r="B429" s="14" t="n">
         <v>10309</v>
       </c>
     </row>
@@ -6780,18 +6791,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B430" s="13">
+      <c r="B430" s="14">
         <f>B425+B429</f>
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="15" t="inlineStr">
+      <c r="A431" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B431" s="16">
+      <c r="B431" s="17">
         <f>B425/B430</f>
         <v/>
       </c>
@@ -6799,22 +6810,22 @@
     <row r="432"/>
     <row r="433"/>
     <row r="434">
-      <c r="A434" s="5" t="inlineStr">
+      <c r="A434" s="6" t="inlineStr">
         <is>
           <t>1-hour call-outs (7)</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="12" t="inlineStr">
+      <c r="A435" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="6" t="inlineStr"/>
-      <c r="B436" s="7" t="inlineStr">
+      <c r="A436" s="7" t="inlineStr"/>
+      <c r="B436" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -6826,7 +6837,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B437" s="13" t="n">
+      <c r="B437" s="14" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6836,7 +6847,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B438" s="13" t="n">
+      <c r="B438" s="14" t="n">
         <v>1141</v>
       </c>
     </row>
@@ -6846,7 +6857,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B439" s="13" t="n">
+      <c r="B439" s="14" t="n">
         <v>1144</v>
       </c>
     </row>
@@ -6856,7 +6867,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B440" s="13">
+      <c r="B440" s="14">
         <f>B438+B439</f>
         <v/>
       </c>
@@ -6867,7 +6878,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B441" s="13" t="n">
+      <c r="B441" s="14" t="n">
         <v>-880</v>
       </c>
     </row>
@@ -6877,7 +6888,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B442" s="13" t="n">
+      <c r="B442" s="14" t="n">
         <v>-476</v>
       </c>
     </row>
@@ -6887,18 +6898,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B443" s="13">
+      <c r="B443" s="14">
         <f>B440+B441+B442</f>
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="15" t="inlineStr">
+      <c r="A444" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B444" s="16">
+      <c r="B444" s="17">
         <f>B443/B440</f>
         <v/>
       </c>
@@ -6906,22 +6917,22 @@
     <row r="445"/>
     <row r="446"/>
     <row r="447">
-      <c r="A447" s="5" t="inlineStr">
+      <c r="A447" s="6" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (11)</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="12" t="inlineStr">
+      <c r="A448" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="6" t="inlineStr"/>
-      <c r="B449" s="7" t="inlineStr">
+      <c r="A449" s="7" t="inlineStr"/>
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -6933,7 +6944,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B450" s="13" t="n">
+      <c r="B450" s="14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6943,7 +6954,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B451" s="13" t="n">
+      <c r="B451" s="14" t="n">
         <v>2686</v>
       </c>
     </row>
@@ -6953,7 +6964,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B452" s="13" t="n">
+      <c r="B452" s="14" t="n">
         <v>2132</v>
       </c>
     </row>
@@ -6963,7 +6974,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B453" s="13">
+      <c r="B453" s="14">
         <f>B451+B452</f>
         <v/>
       </c>
@@ -6974,7 +6985,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B454" s="13" t="n">
+      <c r="B454" s="14" t="n">
         <v>-1640</v>
       </c>
     </row>
@@ -6984,7 +6995,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B455" s="13" t="n">
+      <c r="B455" s="14" t="n">
         <v>-1122</v>
       </c>
     </row>
@@ -6994,18 +7005,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B456" s="13">
+      <c r="B456" s="14">
         <f>B453+B454+B455</f>
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="15" t="inlineStr">
+      <c r="A457" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B457" s="16">
+      <c r="B457" s="17">
         <f>B456/B453</f>
         <v/>
       </c>
@@ -7013,22 +7024,22 @@
     <row r="458"/>
     <row r="459"/>
     <row r="460">
-      <c r="A460" s="5" t="inlineStr">
+      <c r="A460" s="6" t="inlineStr">
         <is>
           <t>2-hour call-outs (8)</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="12" t="inlineStr">
+      <c r="A461" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="6" t="inlineStr"/>
-      <c r="B462" s="7" t="inlineStr">
+      <c r="A462" s="7" t="inlineStr"/>
+      <c r="B462" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7040,7 +7051,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B463" s="13" t="n">
+      <c r="B463" s="14" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7050,7 +7061,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B464" s="13" t="n">
+      <c r="B464" s="14" t="n">
         <v>2608</v>
       </c>
     </row>
@@ -7060,7 +7071,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B465" s="13" t="n">
+      <c r="B465" s="14" t="n">
         <v>1131</v>
       </c>
     </row>
@@ -7070,7 +7081,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B466" s="13">
+      <c r="B466" s="14">
         <f>B464+B465</f>
         <v/>
       </c>
@@ -7081,7 +7092,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B467" s="13" t="n">
+      <c r="B467" s="14" t="n">
         <v>-870</v>
       </c>
     </row>
@@ -7091,7 +7102,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B468" s="13" t="n">
+      <c r="B468" s="14" t="n">
         <v>-1088</v>
       </c>
     </row>
@@ -7101,18 +7112,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B469" s="13">
+      <c r="B469" s="14">
         <f>B466+B467+B468</f>
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="15" t="inlineStr">
+      <c r="A470" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B470" s="16">
+      <c r="B470" s="17">
         <f>B469/B466</f>
         <v/>
       </c>
@@ -7120,22 +7131,22 @@
     <row r="471"/>
     <row r="472"/>
     <row r="473">
-      <c r="A473" s="5" t="inlineStr">
+      <c r="A473" s="6" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (11)</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="12" t="inlineStr">
+      <c r="A474" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="6" t="inlineStr"/>
-      <c r="B475" s="7" t="inlineStr">
+      <c r="A475" s="7" t="inlineStr"/>
+      <c r="B475" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7147,7 +7158,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B476" s="13" t="n">
+      <c r="B476" s="14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7157,7 +7168,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B477" s="13" t="n">
+      <c r="B477" s="14" t="n">
         <v>4485</v>
       </c>
     </row>
@@ -7167,7 +7178,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B478" s="13" t="n">
+      <c r="B478" s="14" t="n">
         <v>2301</v>
       </c>
     </row>
@@ -7177,7 +7188,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B479" s="13">
+      <c r="B479" s="14">
         <f>B477+B478</f>
         <v/>
       </c>
@@ -7188,7 +7199,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B480" s="13" t="n">
+      <c r="B480" s="14" t="n">
         <v>-1770</v>
       </c>
     </row>
@@ -7198,7 +7209,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B481" s="13" t="n">
+      <c r="B481" s="14" t="n">
         <v>-1870</v>
       </c>
     </row>
@@ -7208,18 +7219,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B482" s="13">
+      <c r="B482" s="14">
         <f>B479+B480+B481</f>
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="15" t="inlineStr">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B483" s="16">
+      <c r="B483" s="17">
         <f>B482/B479</f>
         <v/>
       </c>
@@ -7227,22 +7238,22 @@
     <row r="484"/>
     <row r="485"/>
     <row r="486">
-      <c r="A486" s="5" t="inlineStr">
+      <c r="A486" s="6" t="inlineStr">
         <is>
           <t>3-hour call-outs (21)</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="12" t="inlineStr">
+      <c r="A487" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="6" t="inlineStr"/>
-      <c r="B488" s="7" t="inlineStr">
+      <c r="A488" s="7" t="inlineStr"/>
+      <c r="B488" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7254,7 +7265,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B489" s="13" t="n">
+      <c r="B489" s="14" t="n">
         <v>21</v>
       </c>
     </row>
@@ -7264,7 +7275,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B490" s="13" t="n">
+      <c r="B490" s="14" t="n">
         <v>10269</v>
       </c>
     </row>
@@ -7274,7 +7285,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B491" s="13" t="n">
+      <c r="B491" s="14" t="n">
         <v>2899</v>
       </c>
     </row>
@@ -7284,7 +7295,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B492" s="13">
+      <c r="B492" s="14">
         <f>B490+B491</f>
         <v/>
       </c>
@@ -7295,7 +7306,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B493" s="13" t="n">
+      <c r="B493" s="14" t="n">
         <v>-2230</v>
       </c>
     </row>
@@ -7305,7 +7316,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B494" s="13" t="n">
+      <c r="B494" s="14" t="n">
         <v>-4284</v>
       </c>
     </row>
@@ -7315,18 +7326,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B495" s="13">
+      <c r="B495" s="14">
         <f>B492+B493+B494</f>
         <v/>
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="15" t="inlineStr">
+      <c r="A496" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B496" s="16">
+      <c r="B496" s="17">
         <f>B495/B492</f>
         <v/>
       </c>
@@ -7334,22 +7345,22 @@
     <row r="497"/>
     <row r="498"/>
     <row r="499">
-      <c r="A499" s="5" t="inlineStr">
+      <c r="A499" s="6" t="inlineStr">
         <is>
           <t>4-hour call-outs (4)</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="12" t="inlineStr">
+      <c r="A500" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in January, added together</t>
         </is>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="6" t="inlineStr"/>
-      <c r="B501" s="7" t="inlineStr">
+      <c r="A501" s="7" t="inlineStr"/>
+      <c r="B501" s="8" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7361,7 +7372,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B502" s="13" t="n">
+      <c r="B502" s="14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7371,7 +7382,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B503" s="13" t="n">
+      <c r="B503" s="14" t="n">
         <v>2608</v>
       </c>
     </row>
@@ -7381,7 +7392,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B504" s="13" t="n">
+      <c r="B504" s="14" t="n">
         <v>702</v>
       </c>
     </row>
@@ -7391,7 +7402,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B505" s="13">
+      <c r="B505" s="14">
         <f>B503+B504</f>
         <v/>
       </c>
@@ -7402,7 +7413,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B506" s="13" t="n">
+      <c r="B506" s="14" t="n">
         <v>-540</v>
       </c>
     </row>
@@ -7412,7 +7423,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B507" s="13" t="n">
+      <c r="B507" s="14" t="n">
         <v>-1088</v>
       </c>
     </row>
@@ -7422,18 +7433,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B508" s="13">
+      <c r="B508" s="14">
         <f>B505+B506+B507</f>
         <v/>
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="15" t="inlineStr">
+      <c r="A509" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B509" s="16">
+      <c r="B509" s="17">
         <f>B508/B505</f>
         <v/>
       </c>
@@ -7447,7 +7458,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7725,2028 +7736,2028 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>191014</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>114334</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="15">
         <f>IF(D6=0,"",F6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>200124</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>113016</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <f>IF(D7=0,"",F7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>159406</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>85316</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f>IF(D8=0,"",F8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>156794</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>80742</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <f>IF(D9=0,"",F9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>179190</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>102348</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <f>IF(D10=0,"",F10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>150465</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>85752</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <f>IF(D11=0,"",F11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>138865</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>76808</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f>IF(D12=0,"",F12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>144649</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>83700</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <f>IF(D13=0,"",F13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>183265</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>97584</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <f>IF(D14=0,"",F14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>208588</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>120326</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <f>IF(D15=0,"",F15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>155118</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>78258</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f>IF(D16=0,"",F16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>143077</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>80054</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <f>IF(D17=0,"",F17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <f>IF(D18=0,"",F18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>194966</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>115942</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>IF(D19=0,"",F19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>150283</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>84626</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <f>IF(D20=0,"",F20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>183306</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>106590</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <f>IF(D21=0,"",F21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f>IF(D22=0,"",F22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <f>IF(D23=0,"",F23/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <f>IF(D24=0,"",F24/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>IF(D25=0,"",F25/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="15">
         <f>IF(D26=0,"",F26/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <f>IF(D27=0,"",F27/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f>IF(D28=0,"",F28/D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f>IF(D29=0,"",F29/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="14" t="n">
         <v>35720</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="15">
         <f>IF(D30=0,"",F30/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <f>IF(D31=0,"",F31/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="15">
         <f>IF(D32=0,"",F32/D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="15">
         <f>IF(D33=0,"",F33/D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="15">
         <f>IF(D34=0,"",F34/D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="15">
         <f>IF(D35=0,"",F35/D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="15">
         <f>IF(D36=0,"",F36/D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <f>IF(D37=0,"",F37/D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="14" t="n">
         <v>141600</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="14" t="n">
         <v>92430</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="15">
         <f>IF(D38=0,"",F38/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>147100</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>89070</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <f>IF(D39=0,"",F39/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>103700</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>59908</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <f>IF(D40=0,"",F40/D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>100100</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>54678</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <f>IF(D41=0,"",F41/D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="14" t="n">
         <v>118600</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="14" t="n">
         <v>74966</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <f>IF(D42=0,"",F42/D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="14" t="n">
         <v>96400</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="14" t="n">
         <v>61664</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <f>IF(D43=0,"",F43/D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="14" t="n">
         <v>83900</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="14" t="n">
         <v>52264</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <f>IF(D44=0,"",F44/D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="14" t="n">
         <v>89900</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="14" t="n">
         <v>59534</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <f>IF(D45=0,"",F45/D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="14" t="n">
         <v>126300</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="14" t="n">
         <v>72976</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="15">
         <f>IF(D46=0,"",F46/D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="14" t="n">
         <v>152100</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="14" t="n">
         <v>96920</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="15">
         <f>IF(D47=0,"",F47/D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="14" t="n">
         <v>96500</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <v>53590</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="15">
         <f>IF(D48=0,"",F48/D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="14" t="n">
         <v>84200</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="14" t="n">
         <v>55440</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="15">
         <f>IF(D49=0,"",F49/D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f>IF(D50=0,"",F50/D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="14" t="n">
         <v>126900</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="14" t="n">
         <v>87174</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="15">
         <f>IF(D51=0,"",F51/D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>78100</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>53408</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="15">
         <f>IF(D52=0,"",F52/D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="14" t="n">
         <v>109100</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="14" t="n">
         <v>74216</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="15">
         <f>IF(D53=0,"",F53/D53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="14" t="n">
         <v>21764</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="14" t="n">
         <v>11484</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f>IF(D54=0,"",F54/D54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="14" t="n">
         <v>25374</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="14" t="n">
         <v>13526</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="15">
         <f>IF(D55=0,"",F55/D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="14" t="n">
         <v>28056</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="14" t="n">
         <v>14988</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="15">
         <f>IF(D56=0,"",F56/D56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="14" t="n">
         <v>29044</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="14" t="n">
         <v>15644</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="15">
         <f>IF(D57=0,"",F57/D57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="14" t="n">
         <v>29290</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E58" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <f>D58-E58</f>
         <v/>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="15">
         <f>IF(D58=0,"",F58/D58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="14" t="n">
         <v>22765</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="14" t="n">
         <v>12306</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <f>D59-E59</f>
         <v/>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="15">
         <f>IF(D59=0,"",F59/D59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="14" t="n">
         <v>23665</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="14" t="n">
         <v>12762</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <f>D60-E60</f>
         <v/>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="15">
         <f>IF(D60=0,"",F60/D60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="14" t="n">
         <v>23449</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="14" t="n">
         <v>12384</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="14">
         <f>D61-E61</f>
         <v/>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="15">
         <f>IF(D61=0,"",F61/D61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="14" t="n">
         <v>21245</v>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="14" t="n">
         <v>11162</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="14">
         <f>D62-E62</f>
         <v/>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="15">
         <f>IF(D62=0,"",F62/D62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="14" t="n">
         <v>19288</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="14" t="n">
         <v>9960</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="14">
         <f>D63-E63</f>
         <v/>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="15">
         <f>IF(D63=0,"",F63/D63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="14" t="n">
         <v>21418</v>
       </c>
-      <c r="E64" s="13" t="n">
+      <c r="E64" s="14" t="n">
         <v>11222</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="14">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="14">
+      <c r="G64" s="15">
         <f>IF(D64=0,"",F64/D64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="14" t="n">
         <v>21677</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="14" t="n">
         <v>11168</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="14">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="14">
+      <c r="G65" s="15">
         <f>IF(D65=0,"",F65/D65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="14">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="14">
+      <c r="G66" s="15">
         <f>IF(D66=0,"",F66/D66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="14" t="n">
         <v>27966</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="14" t="n">
         <v>14252</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="14">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="14">
+      <c r="G67" s="15">
         <f>IF(D67=0,"",F67/D67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="14" t="n">
         <v>32083</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="14" t="n">
         <v>16702</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="14">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="14">
+      <c r="G68" s="15">
         <f>IF(D68=0,"",F68/D68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="14" t="n">
         <v>34106</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="14" t="n">
         <v>17858</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="14">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="14">
+      <c r="G69" s="15">
         <f>IF(D69=0,"",F69/D69)</f>
         <v/>
       </c>
@@ -9757,7 +9768,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
